--- a/12622343.xlsx
+++ b/12622343.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30431"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30502"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776-26271\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{90E7EE46-5A2B-440B-889A-22320F17AA7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{26A58840-5702-46D0-B866-ED156A8B4599}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="80">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -277,6 +277,9 @@
   </si>
   <si>
     <t>Weekend spent well</t>
+  </si>
+  <si>
+    <t>Just as regular mondays</t>
   </si>
 </sst>
 </file>
@@ -2021,29 +2024,53 @@
         <v>78</v>
       </c>
     </row>
-    <row r="27" spans="1:14">
-      <c r="A27" s="13"/>
-      <c r="B27" s="14"/>
-      <c r="C27" s="14"/>
-      <c r="D27" s="14"/>
-      <c r="E27" s="14"/>
-      <c r="F27" s="14"/>
-      <c r="G27" s="14"/>
-      <c r="H27" s="14"/>
-      <c r="I27" s="15" t="str">
+    <row r="27" spans="1:14" ht="15">
+      <c r="A27" s="13">
+        <v>46272</v>
+      </c>
+      <c r="B27" s="14">
+        <v>400</v>
+      </c>
+      <c r="C27" s="14">
+        <v>30</v>
+      </c>
+      <c r="D27" s="14">
+        <v>200</v>
+      </c>
+      <c r="E27" s="14">
+        <v>150</v>
+      </c>
+      <c r="F27" s="14">
+        <v>200</v>
+      </c>
+      <c r="G27" s="14">
+        <v>4</v>
+      </c>
+      <c r="H27" s="14">
+        <v>120</v>
+      </c>
+      <c r="I27" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J27" s="15" t="str">
+        <v>1100</v>
+      </c>
+      <c r="J27" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K27" s="16"/>
-      <c r="L27" s="16"/>
-      <c r="M27" s="16"/>
-      <c r="N27" s="17"/>
-    </row>
-    <row r="28" spans="1:14">
+        <v>340</v>
+      </c>
+      <c r="K27" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="L27" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="M27" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="N27" s="17" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14" ht="15">
       <c r="A28" s="13"/>
       <c r="B28" s="14"/>
       <c r="C28" s="14"/>

--- a/12622343.xlsx
+++ b/12622343.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776-26271\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{26A58840-5702-46D0-B866-ED156A8B4599}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{30E5C99F-F340-43C6-A30F-6FF48A39AAFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="81">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -280,6 +280,9 @@
   </si>
   <si>
     <t>Just as regular mondays</t>
+  </si>
+  <si>
+    <t>Day went well</t>
   </si>
 </sst>
 </file>
@@ -2071,26 +2074,50 @@
       </c>
     </row>
     <row r="28" spans="1:14" ht="15">
-      <c r="A28" s="13"/>
-      <c r="B28" s="14"/>
-      <c r="C28" s="14"/>
-      <c r="D28" s="14"/>
-      <c r="E28" s="14"/>
-      <c r="F28" s="14"/>
-      <c r="G28" s="14"/>
-      <c r="H28" s="14"/>
-      <c r="I28" s="15" t="str">
+      <c r="A28" s="13">
+        <v>46273</v>
+      </c>
+      <c r="B28" s="14">
+        <v>350</v>
+      </c>
+      <c r="C28" s="14">
+        <v>45</v>
+      </c>
+      <c r="D28" s="14">
+        <v>240</v>
+      </c>
+      <c r="E28" s="14">
+        <v>150</v>
+      </c>
+      <c r="F28" s="14">
+        <v>250</v>
+      </c>
+      <c r="G28" s="14">
+        <v>5</v>
+      </c>
+      <c r="H28" s="14">
+        <v>150</v>
+      </c>
+      <c r="I28" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J28" s="15" t="str">
+        <v>1185</v>
+      </c>
+      <c r="J28" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K28" s="16"/>
-      <c r="L28" s="16"/>
-      <c r="M28" s="16"/>
-      <c r="N28" s="17"/>
+        <v>255</v>
+      </c>
+      <c r="K28" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="L28" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="M28" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="N28" s="17" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="29" spans="1:14">
       <c r="A29" s="13"/>

--- a/12622343.xlsx
+++ b/12622343.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776-26271\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{30E5C99F-F340-43C6-A30F-6FF48A39AAFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{73BFA918-1EC3-4120-874D-7110601CD707}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="83">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -283,6 +283,12 @@
   </si>
   <si>
     <t>Day went well</t>
+  </si>
+  <si>
+    <t>It was a decent day</t>
+  </si>
+  <si>
+    <t>Day went okay</t>
   </si>
 </sst>
 </file>
@@ -2119,49 +2125,97 @@
         <v>80</v>
       </c>
     </row>
-    <row r="29" spans="1:14">
-      <c r="A29" s="13"/>
-      <c r="B29" s="14"/>
-      <c r="C29" s="14"/>
-      <c r="D29" s="14"/>
-      <c r="E29" s="14"/>
-      <c r="F29" s="14"/>
-      <c r="G29" s="14"/>
-      <c r="H29" s="14"/>
-      <c r="I29" s="15" t="str">
+    <row r="29" spans="1:14" ht="15">
+      <c r="A29" s="13">
+        <v>46274</v>
+      </c>
+      <c r="B29" s="14">
+        <v>350</v>
+      </c>
+      <c r="C29" s="14">
+        <v>45</v>
+      </c>
+      <c r="D29" s="14">
+        <v>300</v>
+      </c>
+      <c r="E29" s="14">
+        <v>60</v>
+      </c>
+      <c r="F29" s="14">
+        <v>250</v>
+      </c>
+      <c r="G29" s="14">
+        <v>5</v>
+      </c>
+      <c r="H29" s="14">
+        <v>150</v>
+      </c>
+      <c r="I29" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J29" s="15" t="str">
+        <v>1155</v>
+      </c>
+      <c r="J29" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K29" s="16"/>
-      <c r="L29" s="16"/>
-      <c r="M29" s="16"/>
-      <c r="N29" s="17"/>
-    </row>
-    <row r="30" spans="1:14">
-      <c r="A30" s="13"/>
-      <c r="B30" s="14"/>
-      <c r="C30" s="14"/>
-      <c r="D30" s="14"/>
-      <c r="E30" s="14"/>
-      <c r="F30" s="14"/>
-      <c r="G30" s="14"/>
-      <c r="H30" s="14"/>
-      <c r="I30" s="15" t="str">
+        <v>285</v>
+      </c>
+      <c r="K29" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="L29" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="M29" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="N29" s="17" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14" ht="15">
+      <c r="A30" s="13">
+        <v>46275</v>
+      </c>
+      <c r="B30" s="14">
+        <v>400</v>
+      </c>
+      <c r="C30" s="14">
+        <v>45</v>
+      </c>
+      <c r="D30" s="14">
+        <v>300</v>
+      </c>
+      <c r="E30" s="14">
+        <v>120</v>
+      </c>
+      <c r="F30" s="14">
+        <v>300</v>
+      </c>
+      <c r="G30" s="14">
+        <v>6</v>
+      </c>
+      <c r="H30" s="14">
+        <v>120</v>
+      </c>
+      <c r="I30" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J30" s="15" t="str">
+        <v>1285</v>
+      </c>
+      <c r="J30" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K30" s="16"/>
-      <c r="L30" s="16"/>
-      <c r="M30" s="16"/>
-      <c r="N30" s="17"/>
+        <v>155</v>
+      </c>
+      <c r="K30" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L30" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="M30" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="N30" s="17" t="s">
+        <v>82</v>
+      </c>
     </row>
     <row r="31" spans="1:14">
       <c r="A31" s="13"/>

--- a/12622343.xlsx
+++ b/12622343.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776-26271\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{73BFA918-1EC3-4120-874D-7110601CD707}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D5F98268-8350-4DE5-B242-2F600B36484A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="85">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -289,6 +289,12 @@
   </si>
   <si>
     <t>Day went okay</t>
+  </si>
+  <si>
+    <t>Classes felt hectic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Went for the movies with friends </t>
   </si>
 </sst>
 </file>
@@ -2217,49 +2223,97 @@
         <v>82</v>
       </c>
     </row>
-    <row r="31" spans="1:14">
-      <c r="A31" s="13"/>
-      <c r="B31" s="14"/>
-      <c r="C31" s="14"/>
-      <c r="D31" s="14"/>
-      <c r="E31" s="14"/>
-      <c r="F31" s="14"/>
-      <c r="G31" s="14"/>
-      <c r="H31" s="14"/>
-      <c r="I31" s="15" t="str">
+    <row r="31" spans="1:14" ht="15">
+      <c r="A31" s="13">
+        <v>46276</v>
+      </c>
+      <c r="B31" s="14">
+        <v>240</v>
+      </c>
+      <c r="C31" s="14">
+        <v>30</v>
+      </c>
+      <c r="D31" s="14">
+        <v>200</v>
+      </c>
+      <c r="E31" s="14">
+        <v>120</v>
+      </c>
+      <c r="F31" s="14">
+        <v>350</v>
+      </c>
+      <c r="G31" s="14">
+        <v>7</v>
+      </c>
+      <c r="H31" s="14">
+        <v>100</v>
+      </c>
+      <c r="I31" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J31" s="15" t="str">
+        <v>1040</v>
+      </c>
+      <c r="J31" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K31" s="16"/>
-      <c r="L31" s="16"/>
-      <c r="M31" s="16"/>
-      <c r="N31" s="17"/>
-    </row>
-    <row r="32" spans="1:14">
-      <c r="A32" s="13"/>
-      <c r="B32" s="14"/>
-      <c r="C32" s="14"/>
-      <c r="D32" s="14"/>
-      <c r="E32" s="14"/>
-      <c r="F32" s="14"/>
-      <c r="G32" s="14"/>
-      <c r="H32" s="14"/>
-      <c r="I32" s="15" t="str">
+        <v>400</v>
+      </c>
+      <c r="K31" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="L31" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="M31" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="N31" s="17" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14" ht="30.75">
+      <c r="A32" s="13">
+        <v>46277</v>
+      </c>
+      <c r="B32" s="14">
+        <v>400</v>
+      </c>
+      <c r="C32" s="14">
+        <v>30</v>
+      </c>
+      <c r="D32" s="14">
+        <v>120</v>
+      </c>
+      <c r="E32" s="14">
+        <v>60</v>
+      </c>
+      <c r="F32" s="14">
+        <v>0</v>
+      </c>
+      <c r="G32" s="14">
+        <v>0</v>
+      </c>
+      <c r="H32" s="14">
+        <v>300</v>
+      </c>
+      <c r="I32" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J32" s="15" t="str">
+        <v>910</v>
+      </c>
+      <c r="J32" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K32" s="16"/>
-      <c r="L32" s="16"/>
-      <c r="M32" s="16"/>
-      <c r="N32" s="17"/>
+        <v>530</v>
+      </c>
+      <c r="K32" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="L32" s="16" t="s">
+        <v>69</v>
+      </c>
+      <c r="M32" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="N32" s="17" t="s">
+        <v>84</v>
+      </c>
     </row>
     <row r="33" spans="1:14">
       <c r="A33" s="13"/>

--- a/12622343.xlsx
+++ b/12622343.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776-26271\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D5F98268-8350-4DE5-B242-2F600B36484A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D680F39F-5EF8-43BA-B95F-1B88A9CEAC98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="85">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2315,27 +2315,51 @@
         <v>84</v>
       </c>
     </row>
-    <row r="33" spans="1:14">
-      <c r="A33" s="13"/>
-      <c r="B33" s="14"/>
-      <c r="C33" s="14"/>
-      <c r="D33" s="14"/>
-      <c r="E33" s="14"/>
-      <c r="F33" s="14"/>
-      <c r="G33" s="14"/>
-      <c r="H33" s="14"/>
-      <c r="I33" s="15" t="str">
+    <row r="33" spans="1:14" ht="15">
+      <c r="A33" s="13">
+        <v>46278</v>
+      </c>
+      <c r="B33" s="14">
+        <v>450</v>
+      </c>
+      <c r="C33" s="14">
+        <v>30</v>
+      </c>
+      <c r="D33" s="14">
+        <v>240</v>
+      </c>
+      <c r="E33" s="14">
+        <v>60</v>
+      </c>
+      <c r="F33" s="14">
+        <v>0</v>
+      </c>
+      <c r="G33" s="14">
+        <v>0</v>
+      </c>
+      <c r="H33" s="14">
+        <v>120</v>
+      </c>
+      <c r="I33" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J33" s="15" t="str">
+        <v>900</v>
+      </c>
+      <c r="J33" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K33" s="16"/>
-      <c r="L33" s="16"/>
-      <c r="M33" s="16"/>
-      <c r="N33" s="17"/>
+        <v>540</v>
+      </c>
+      <c r="K33" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="L33" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="M33" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="N33" s="17" t="s">
+        <v>78</v>
+      </c>
     </row>
     <row r="34" spans="1:14">
       <c r="A34" s="13"/>

--- a/12622343.xlsx
+++ b/12622343.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776-26271\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D680F39F-5EF8-43BA-B95F-1B88A9CEAC98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6E3CECD5-7BC8-46A9-9630-16A28C4A2E26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="85">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2361,27 +2361,51 @@
         <v>78</v>
       </c>
     </row>
-    <row r="34" spans="1:14">
-      <c r="A34" s="13"/>
-      <c r="B34" s="14"/>
-      <c r="C34" s="14"/>
-      <c r="D34" s="14"/>
-      <c r="E34" s="14"/>
-      <c r="F34" s="14"/>
-      <c r="G34" s="14"/>
-      <c r="H34" s="14"/>
-      <c r="I34" s="15" t="str">
+    <row r="34" spans="1:14" ht="15">
+      <c r="A34" s="13">
+        <v>46279</v>
+      </c>
+      <c r="B34" s="14">
+        <v>300</v>
+      </c>
+      <c r="C34" s="14">
+        <v>40</v>
+      </c>
+      <c r="D34" s="14">
+        <v>200</v>
+      </c>
+      <c r="E34" s="14">
+        <v>100</v>
+      </c>
+      <c r="F34" s="14">
+        <v>200</v>
+      </c>
+      <c r="G34" s="14">
+        <v>4</v>
+      </c>
+      <c r="H34" s="14">
+        <v>200</v>
+      </c>
+      <c r="I34" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J34" s="15" t="str">
+        <v>1040</v>
+      </c>
+      <c r="J34" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K34" s="16"/>
-      <c r="L34" s="16"/>
-      <c r="M34" s="16"/>
-      <c r="N34" s="17"/>
+        <v>400</v>
+      </c>
+      <c r="K34" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="L34" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="M34" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="N34" s="17" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="35" spans="1:14">
       <c r="A35" s="13"/>

--- a/12622343.xlsx
+++ b/12622343.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776-26271\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6E3CECD5-7BC8-46A9-9630-16A28C4A2E26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{DDF4D710-59C6-41E3-9907-90DE79757CCE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="86">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -295,6 +295,9 @@
   </si>
   <si>
     <t xml:space="preserve">Went for the movies with friends </t>
+  </si>
+  <si>
+    <t>Felt tired after classes</t>
   </si>
 </sst>
 </file>
@@ -2407,27 +2410,51 @@
         <v>67</v>
       </c>
     </row>
-    <row r="35" spans="1:14">
-      <c r="A35" s="13"/>
-      <c r="B35" s="14"/>
-      <c r="C35" s="14"/>
-      <c r="D35" s="14"/>
-      <c r="E35" s="14"/>
-      <c r="F35" s="14"/>
-      <c r="G35" s="14"/>
-      <c r="H35" s="14"/>
-      <c r="I35" s="15" t="str">
+    <row r="35" spans="1:14" ht="15">
+      <c r="A35" s="13">
+        <v>46280</v>
+      </c>
+      <c r="B35" s="14">
+        <v>400</v>
+      </c>
+      <c r="C35" s="14">
+        <v>30</v>
+      </c>
+      <c r="D35" s="14">
+        <v>240</v>
+      </c>
+      <c r="E35" s="14">
+        <v>120</v>
+      </c>
+      <c r="F35" s="14">
+        <v>250</v>
+      </c>
+      <c r="G35" s="14">
+        <v>5</v>
+      </c>
+      <c r="H35" s="14">
+        <v>120</v>
+      </c>
+      <c r="I35" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J35" s="15" t="str">
+        <v>1160</v>
+      </c>
+      <c r="J35" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K35" s="16"/>
-      <c r="L35" s="16"/>
-      <c r="M35" s="16"/>
-      <c r="N35" s="17"/>
+        <v>280</v>
+      </c>
+      <c r="K35" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="L35" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="M35" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="N35" s="17" t="s">
+        <v>85</v>
+      </c>
     </row>
     <row r="36" spans="1:14">
       <c r="A36" s="13"/>

--- a/12622343.xlsx
+++ b/12622343.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776-26271\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DDF4D710-59C6-41E3-9907-90DE79757CCE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A88C74EE-E97C-4DD2-9673-B993D952C1AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="86">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2456,27 +2456,51 @@
         <v>85</v>
       </c>
     </row>
-    <row r="36" spans="1:14">
-      <c r="A36" s="13"/>
-      <c r="B36" s="14"/>
-      <c r="C36" s="14"/>
-      <c r="D36" s="14"/>
-      <c r="E36" s="14"/>
-      <c r="F36" s="14"/>
-      <c r="G36" s="14"/>
-      <c r="H36" s="14"/>
-      <c r="I36" s="15" t="str">
+    <row r="36" spans="1:14" ht="15">
+      <c r="A36" s="13">
+        <v>46281</v>
+      </c>
+      <c r="B36" s="14">
+        <v>350</v>
+      </c>
+      <c r="C36" s="14">
+        <v>100</v>
+      </c>
+      <c r="D36" s="14">
+        <v>200</v>
+      </c>
+      <c r="E36" s="14">
+        <v>120</v>
+      </c>
+      <c r="F36" s="14">
+        <v>250</v>
+      </c>
+      <c r="G36" s="14">
+        <v>5</v>
+      </c>
+      <c r="H36" s="14">
+        <v>100</v>
+      </c>
+      <c r="I36" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J36" s="15" t="str">
+        <v>1120</v>
+      </c>
+      <c r="J36" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K36" s="16"/>
-      <c r="L36" s="16"/>
-      <c r="M36" s="16"/>
-      <c r="N36" s="17"/>
+        <v>320</v>
+      </c>
+      <c r="K36" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="L36" s="16" t="s">
+        <v>69</v>
+      </c>
+      <c r="M36" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="N36" s="17" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="37" spans="1:14">
       <c r="A37" s="13"/>

--- a/12622343.xlsx
+++ b/12622343.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30502"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30509"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776-26271\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A88C74EE-E97C-4DD2-9673-B993D952C1AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{4E7081A1-27C4-41D2-BEE2-EF62CEF76276}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="86">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2502,27 +2502,51 @@
         <v>71</v>
       </c>
     </row>
-    <row r="37" spans="1:14">
-      <c r="A37" s="13"/>
-      <c r="B37" s="14"/>
-      <c r="C37" s="14"/>
-      <c r="D37" s="14"/>
-      <c r="E37" s="14"/>
-      <c r="F37" s="14"/>
-      <c r="G37" s="14"/>
-      <c r="H37" s="14"/>
-      <c r="I37" s="15" t="str">
+    <row r="37" spans="1:14" ht="15">
+      <c r="A37" s="13">
+        <v>46282</v>
+      </c>
+      <c r="B37" s="14">
+        <v>320</v>
+      </c>
+      <c r="C37" s="14">
+        <v>40</v>
+      </c>
+      <c r="D37" s="14">
+        <v>200</v>
+      </c>
+      <c r="E37" s="14">
+        <v>120</v>
+      </c>
+      <c r="F37" s="14">
+        <v>300</v>
+      </c>
+      <c r="G37" s="14">
+        <v>6</v>
+      </c>
+      <c r="H37" s="14">
+        <v>100</v>
+      </c>
+      <c r="I37" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J37" s="15" t="str">
+        <v>1080</v>
+      </c>
+      <c r="J37" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K37" s="16"/>
-      <c r="L37" s="16"/>
-      <c r="M37" s="16"/>
-      <c r="N37" s="17"/>
+        <v>360</v>
+      </c>
+      <c r="K37" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="L37" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="M37" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="N37" s="17" t="s">
+        <v>75</v>
+      </c>
     </row>
     <row r="38" spans="1:14">
       <c r="A38" s="13"/>

--- a/12622343.xlsx
+++ b/12622343.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30509"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30516"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776-26271\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4E7081A1-27C4-41D2-BEE2-EF62CEF76276}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{DD483B85-00D1-4294-A266-62D8B778D937}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="87">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -298,6 +298,9 @@
   </si>
   <si>
     <t>Felt tired after classes</t>
+  </si>
+  <si>
+    <t>Day went descent</t>
   </si>
 </sst>
 </file>
@@ -2545,30 +2548,54 @@
         <v>63</v>
       </c>
       <c r="N37" s="17" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="38" spans="1:14">
-      <c r="A38" s="13"/>
-      <c r="B38" s="14"/>
-      <c r="C38" s="14"/>
-      <c r="D38" s="14"/>
-      <c r="E38" s="14"/>
-      <c r="F38" s="14"/>
-      <c r="G38" s="14"/>
-      <c r="H38" s="14"/>
-      <c r="I38" s="15" t="str">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="38" spans="1:14" ht="15">
+      <c r="A38" s="13">
+        <v>46283</v>
+      </c>
+      <c r="B38" s="14">
+        <v>360</v>
+      </c>
+      <c r="C38" s="14">
+        <v>30</v>
+      </c>
+      <c r="D38" s="14">
+        <v>120</v>
+      </c>
+      <c r="E38" s="14">
+        <v>120</v>
+      </c>
+      <c r="F38" s="14">
+        <v>350</v>
+      </c>
+      <c r="G38" s="14">
+        <v>7</v>
+      </c>
+      <c r="H38" s="14">
+        <v>120</v>
+      </c>
+      <c r="I38" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J38" s="15" t="str">
+        <v>1100</v>
+      </c>
+      <c r="J38" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K38" s="16"/>
-      <c r="L38" s="16"/>
-      <c r="M38" s="16"/>
-      <c r="N38" s="17"/>
+        <v>340</v>
+      </c>
+      <c r="K38" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="L38" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="M38" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="N38" s="17" t="s">
+        <v>83</v>
+      </c>
     </row>
     <row r="39" spans="1:14">
       <c r="A39" s="13"/>

--- a/12622343.xlsx
+++ b/12622343.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776-26271\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DD483B85-00D1-4294-A266-62D8B778D937}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{7167D335-EE29-4E0B-8FD9-023789297EB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="87">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2597,27 +2597,51 @@
         <v>83</v>
       </c>
     </row>
-    <row r="39" spans="1:14">
-      <c r="A39" s="13"/>
-      <c r="B39" s="14"/>
-      <c r="C39" s="14"/>
-      <c r="D39" s="14"/>
-      <c r="E39" s="14"/>
-      <c r="F39" s="14"/>
-      <c r="G39" s="14"/>
-      <c r="H39" s="14"/>
-      <c r="I39" s="15" t="str">
+    <row r="39" spans="1:14" ht="15">
+      <c r="A39" s="13">
+        <v>46284</v>
+      </c>
+      <c r="B39" s="14">
+        <v>450</v>
+      </c>
+      <c r="C39" s="14">
+        <v>45</v>
+      </c>
+      <c r="D39" s="14">
+        <v>180</v>
+      </c>
+      <c r="E39" s="14">
+        <v>120</v>
+      </c>
+      <c r="F39" s="14">
+        <v>50</v>
+      </c>
+      <c r="G39" s="14">
+        <v>1</v>
+      </c>
+      <c r="H39" s="14">
+        <v>150</v>
+      </c>
+      <c r="I39" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J39" s="15" t="str">
+        <v>995</v>
+      </c>
+      <c r="J39" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K39" s="16"/>
-      <c r="L39" s="16"/>
-      <c r="M39" s="16"/>
-      <c r="N39" s="17"/>
+        <v>445</v>
+      </c>
+      <c r="K39" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="L39" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="M39" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="N39" s="17" t="s">
+        <v>75</v>
+      </c>
     </row>
     <row r="40" spans="1:14">
       <c r="A40" s="13"/>

--- a/12622343.xlsx
+++ b/12622343.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776-26271\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7167D335-EE29-4E0B-8FD9-023789297EB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A3E049EC-FF09-42DD-808C-227C999FBDF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="88">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -301,6 +301,9 @@
   </si>
   <si>
     <t>Day went descent</t>
+  </si>
+  <si>
+    <t>Had a personal gtooming session today</t>
   </si>
 </sst>
 </file>
@@ -2643,27 +2646,51 @@
         <v>75</v>
       </c>
     </row>
-    <row r="40" spans="1:14">
-      <c r="A40" s="13"/>
-      <c r="B40" s="14"/>
-      <c r="C40" s="14"/>
-      <c r="D40" s="14"/>
-      <c r="E40" s="14"/>
-      <c r="F40" s="14"/>
-      <c r="G40" s="14"/>
-      <c r="H40" s="14"/>
-      <c r="I40" s="15" t="str">
+    <row r="40" spans="1:14" ht="30.75">
+      <c r="A40" s="13">
+        <v>46285</v>
+      </c>
+      <c r="B40" s="14">
+        <v>400</v>
+      </c>
+      <c r="C40" s="14">
+        <v>100</v>
+      </c>
+      <c r="D40" s="14">
+        <v>200</v>
+      </c>
+      <c r="E40" s="14">
+        <v>120</v>
+      </c>
+      <c r="F40" s="14">
+        <v>0</v>
+      </c>
+      <c r="G40" s="14">
+        <v>0</v>
+      </c>
+      <c r="H40" s="14">
+        <v>200</v>
+      </c>
+      <c r="I40" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J40" s="15" t="str">
+        <v>1020</v>
+      </c>
+      <c r="J40" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K40" s="16"/>
-      <c r="L40" s="16"/>
-      <c r="M40" s="16"/>
-      <c r="N40" s="17"/>
+        <v>420</v>
+      </c>
+      <c r="K40" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="L40" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="M40" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="N40" s="17" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="41" spans="1:14">
       <c r="A41" s="13"/>

--- a/12622343.xlsx
+++ b/12622343.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776-26271\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A3E049EC-FF09-42DD-808C-227C999FBDF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{AF4EB851-FB1C-4BD0-86FD-F7EA3A6CAFD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="89">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -303,7 +303,10 @@
     <t>Day went descent</t>
   </si>
   <si>
-    <t>Had a personal gtooming session today</t>
+    <t>Had a personal grooming session today</t>
+  </si>
+  <si>
+    <t>Felt low on energy today</t>
   </si>
 </sst>
 </file>
@@ -2692,27 +2695,51 @@
         <v>87</v>
       </c>
     </row>
-    <row r="41" spans="1:14">
-      <c r="A41" s="13"/>
-      <c r="B41" s="14"/>
-      <c r="C41" s="14"/>
-      <c r="D41" s="14"/>
-      <c r="E41" s="14"/>
-      <c r="F41" s="14"/>
-      <c r="G41" s="14"/>
-      <c r="H41" s="14"/>
-      <c r="I41" s="15" t="str">
+    <row r="41" spans="1:14" ht="15">
+      <c r="A41" s="13">
+        <v>46286</v>
+      </c>
+      <c r="B41" s="14">
+        <v>350</v>
+      </c>
+      <c r="C41" s="14">
+        <v>100</v>
+      </c>
+      <c r="D41" s="14">
+        <v>180</v>
+      </c>
+      <c r="E41" s="14">
+        <v>120</v>
+      </c>
+      <c r="F41" s="14">
+        <v>200</v>
+      </c>
+      <c r="G41" s="14">
+        <v>4</v>
+      </c>
+      <c r="H41" s="14">
+        <v>200</v>
+      </c>
+      <c r="I41" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J41" s="15" t="str">
+        <v>1150</v>
+      </c>
+      <c r="J41" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K41" s="16"/>
-      <c r="L41" s="16"/>
-      <c r="M41" s="16"/>
-      <c r="N41" s="17"/>
+        <v>290</v>
+      </c>
+      <c r="K41" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="L41" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="M41" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="N41" s="17" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="42" spans="1:14">
       <c r="A42" s="13"/>

--- a/12622343.xlsx
+++ b/12622343.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776-26271\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{AF4EB851-FB1C-4BD0-86FD-F7EA3A6CAFD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E8926B43-53FC-4C46-8A7F-7537665D66E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="90">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -307,6 +307,9 @@
   </si>
   <si>
     <t>Felt low on energy today</t>
+  </si>
+  <si>
+    <t>Was having continuous headaches throughout the day</t>
   </si>
 </sst>
 </file>
@@ -2741,27 +2744,51 @@
         <v>88</v>
       </c>
     </row>
-    <row r="42" spans="1:14">
-      <c r="A42" s="13"/>
-      <c r="B42" s="14"/>
-      <c r="C42" s="14"/>
-      <c r="D42" s="14"/>
-      <c r="E42" s="14"/>
-      <c r="F42" s="14"/>
-      <c r="G42" s="14"/>
-      <c r="H42" s="14"/>
-      <c r="I42" s="15" t="str">
+    <row r="42" spans="1:14" ht="30.75">
+      <c r="A42" s="13">
+        <v>46287</v>
+      </c>
+      <c r="B42" s="14">
+        <v>300</v>
+      </c>
+      <c r="C42" s="14">
+        <v>100</v>
+      </c>
+      <c r="D42" s="14">
+        <v>180</v>
+      </c>
+      <c r="E42" s="14">
+        <v>120</v>
+      </c>
+      <c r="F42" s="14">
+        <v>300</v>
+      </c>
+      <c r="G42" s="14">
+        <v>5</v>
+      </c>
+      <c r="H42" s="14">
+        <v>200</v>
+      </c>
+      <c r="I42" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J42" s="15" t="str">
+        <v>1200</v>
+      </c>
+      <c r="J42" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K42" s="16"/>
-      <c r="L42" s="16"/>
-      <c r="M42" s="16"/>
-      <c r="N42" s="17"/>
+        <v>240</v>
+      </c>
+      <c r="K42" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="L42" s="16" t="s">
+        <v>69</v>
+      </c>
+      <c r="M42" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="N42" s="17" t="s">
+        <v>89</v>
+      </c>
     </row>
     <row r="43" spans="1:14">
       <c r="A43" s="13"/>

--- a/12622343.xlsx
+++ b/12622343.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776-26271\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E8926B43-53FC-4C46-8A7F-7537665D66E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C84CEF22-9F73-443F-BE2F-6480636E772D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="92">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -306,10 +306,16 @@
     <t>Had a personal grooming session today</t>
   </si>
   <si>
+    <t>Low</t>
+  </si>
+  <si>
     <t>Felt low on energy today</t>
   </si>
   <si>
     <t>Was having continuous headaches throughout the day</t>
+  </si>
+  <si>
+    <t>Got stung by a bee today</t>
   </si>
 </sst>
 </file>
@@ -2738,10 +2744,10 @@
         <v>54</v>
       </c>
       <c r="M41" s="16" t="s">
-        <v>63</v>
+        <v>88</v>
       </c>
       <c r="N41" s="17" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="42" spans="1:14" ht="30.75">
@@ -2761,7 +2767,7 @@
         <v>120</v>
       </c>
       <c r="F42" s="14">
-        <v>300</v>
+        <v>250</v>
       </c>
       <c r="G42" s="14">
         <v>5</v>
@@ -2771,11 +2777,11 @@
       </c>
       <c r="I42" s="15">
         <f t="shared" si="0"/>
-        <v>1200</v>
+        <v>1150</v>
       </c>
       <c r="J42" s="15">
         <f t="shared" si="1"/>
-        <v>240</v>
+        <v>290</v>
       </c>
       <c r="K42" s="16" t="s">
         <v>53</v>
@@ -2787,30 +2793,54 @@
         <v>63</v>
       </c>
       <c r="N42" s="17" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="43" spans="1:14">
-      <c r="A43" s="13"/>
-      <c r="B43" s="14"/>
-      <c r="C43" s="14"/>
-      <c r="D43" s="14"/>
-      <c r="E43" s="14"/>
-      <c r="F43" s="14"/>
-      <c r="G43" s="14"/>
-      <c r="H43" s="14"/>
-      <c r="I43" s="15" t="str">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="43" spans="1:14" ht="15">
+      <c r="A43" s="13">
+        <v>46288</v>
+      </c>
+      <c r="B43" s="14">
+        <v>300</v>
+      </c>
+      <c r="C43" s="14">
+        <v>45</v>
+      </c>
+      <c r="D43" s="14">
+        <v>120</v>
+      </c>
+      <c r="E43" s="14">
+        <v>100</v>
+      </c>
+      <c r="F43" s="14">
+        <v>250</v>
+      </c>
+      <c r="G43" s="14">
+        <v>5</v>
+      </c>
+      <c r="H43" s="14">
+        <v>200</v>
+      </c>
+      <c r="I43" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J43" s="15" t="str">
+        <v>1015</v>
+      </c>
+      <c r="J43" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K43" s="16"/>
-      <c r="L43" s="16"/>
-      <c r="M43" s="16"/>
-      <c r="N43" s="17"/>
+        <v>425</v>
+      </c>
+      <c r="K43" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="L43" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="M43" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="N43" s="17" t="s">
+        <v>91</v>
+      </c>
     </row>
     <row r="44" spans="1:14">
       <c r="A44" s="13"/>

--- a/12622343.xlsx
+++ b/12622343.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776-26271\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C84CEF22-9F73-443F-BE2F-6480636E772D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{582F9A85-F471-4164-9F63-FE913C82987E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="92">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2842,27 +2842,51 @@
         <v>91</v>
       </c>
     </row>
-    <row r="44" spans="1:14">
-      <c r="A44" s="13"/>
-      <c r="B44" s="14"/>
-      <c r="C44" s="14"/>
-      <c r="D44" s="14"/>
-      <c r="E44" s="14"/>
-      <c r="F44" s="14"/>
-      <c r="G44" s="14"/>
-      <c r="H44" s="14"/>
-      <c r="I44" s="15" t="str">
+    <row r="44" spans="1:14" ht="15">
+      <c r="A44" s="13">
+        <v>46289</v>
+      </c>
+      <c r="B44" s="14">
+        <v>350</v>
+      </c>
+      <c r="C44" s="14">
+        <v>45</v>
+      </c>
+      <c r="D44" s="14">
+        <v>120</v>
+      </c>
+      <c r="E44" s="14">
+        <v>120</v>
+      </c>
+      <c r="F44" s="14">
+        <v>300</v>
+      </c>
+      <c r="G44" s="14">
+        <v>6</v>
+      </c>
+      <c r="H44" s="14">
+        <v>200</v>
+      </c>
+      <c r="I44" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J44" s="15" t="str">
+        <v>1135</v>
+      </c>
+      <c r="J44" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K44" s="16"/>
-      <c r="L44" s="16"/>
-      <c r="M44" s="16"/>
-      <c r="N44" s="17"/>
+        <v>305</v>
+      </c>
+      <c r="K44" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="L44" s="16" t="s">
+        <v>69</v>
+      </c>
+      <c r="M44" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="N44" s="17" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="45" spans="1:14">
       <c r="A45" s="13"/>

--- a/12622343.xlsx
+++ b/12622343.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776-26271\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{582F9A85-F471-4164-9F63-FE913C82987E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{68D69EC7-6CA4-42AB-9330-B102CD2557C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="95">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -156,7 +156,7 @@
     <t>September</t>
   </si>
   <si>
-    <t>All durations in MINUTES. Yellow cells = enter your data. Row 6 is a sample — overwrite it. Rows 2-3: fill your details.</t>
+    <t xml:space="preserve"> </t>
   </si>
   <si>
     <t>Date</t>
@@ -217,6 +217,9 @@
   </si>
   <si>
     <t>Neutral</t>
+  </si>
+  <si>
+    <t>Felt hectic</t>
   </si>
   <si>
     <t>Felt a biit tired after the Evening Activities</t>
@@ -316,6 +319,12 @@
   </si>
   <si>
     <t>Got stung by a bee today</t>
+  </si>
+  <si>
+    <t>Got back to back classes</t>
+  </si>
+  <si>
+    <t>Completed a project today</t>
   </si>
 </sst>
 </file>
@@ -1140,38 +1149,38 @@
         <v>56</v>
       </c>
     </row>
-    <row r="7" spans="1:14" ht="30.75">
+    <row r="7" spans="1:14" ht="15">
       <c r="A7" s="13">
-        <v>46252</v>
+        <v>46251</v>
       </c>
       <c r="B7" s="14">
-        <v>420</v>
+        <v>400</v>
       </c>
       <c r="C7" s="14">
         <v>30</v>
       </c>
       <c r="D7" s="14">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="E7" s="14">
         <v>60</v>
       </c>
       <c r="F7" s="14">
-        <v>300</v>
+        <v>250</v>
       </c>
       <c r="G7" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H7" s="14">
         <v>60</v>
       </c>
       <c r="I7" s="15">
-        <f t="shared" si="0"/>
-        <v>930</v>
+        <f>IF(SUM(B7:F7,H7)=0,"",SUM(B7:F7,H7))</f>
+        <v>900</v>
       </c>
       <c r="J7" s="15">
-        <f t="shared" si="1"/>
-        <v>510</v>
+        <f>IF(I7="","",1440-I7)</f>
+        <v>540</v>
       </c>
       <c r="K7" s="16" t="s">
         <v>57</v>
@@ -1186,12 +1195,12 @@
         <v>59</v>
       </c>
     </row>
-    <row r="8" spans="1:14" ht="15">
+    <row r="8" spans="1:14" ht="30.75">
       <c r="A8" s="13">
-        <v>46253</v>
+        <v>46252</v>
       </c>
       <c r="B8" s="14">
-        <v>400</v>
+        <v>420</v>
       </c>
       <c r="C8" s="14">
         <v>30</v>
@@ -1203,24 +1212,24 @@
         <v>60</v>
       </c>
       <c r="F8" s="14">
-        <v>350</v>
+        <v>300</v>
       </c>
       <c r="G8" s="14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H8" s="14">
         <v>60</v>
       </c>
       <c r="I8" s="15">
-        <f t="shared" si="0"/>
-        <v>960</v>
+        <f>IF(SUM(B8:F8,H8)=0,"",SUM(B8:F8,H8))</f>
+        <v>930</v>
       </c>
       <c r="J8" s="15">
-        <f t="shared" si="1"/>
-        <v>480</v>
+        <f>IF(I8="","",1440-I8)</f>
+        <v>510</v>
       </c>
       <c r="K8" s="16" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="L8" s="16" t="s">
         <v>58</v>
@@ -1234,10 +1243,10 @@
     </row>
     <row r="9" spans="1:14" ht="15">
       <c r="A9" s="13">
-        <v>46254</v>
+        <v>46253</v>
       </c>
       <c r="B9" s="14">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="C9" s="14">
         <v>30</v>
@@ -1249,21 +1258,21 @@
         <v>60</v>
       </c>
       <c r="F9" s="14">
-        <v>300</v>
+        <v>350</v>
       </c>
       <c r="G9" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H9" s="14">
         <v>60</v>
       </c>
       <c r="I9" s="15">
-        <f t="shared" si="0"/>
-        <v>1010</v>
+        <f>IF(SUM(B9:F9,H9)=0,"",SUM(B9:F9,H9))</f>
+        <v>960</v>
       </c>
       <c r="J9" s="15">
-        <f t="shared" si="1"/>
-        <v>430</v>
+        <f>IF(I9="","",1440-I9)</f>
+        <v>480</v>
       </c>
       <c r="K9" s="16" t="s">
         <v>53</v>
@@ -1280,10 +1289,10 @@
     </row>
     <row r="10" spans="1:14" ht="15">
       <c r="A10" s="13">
-        <v>46255</v>
+        <v>46254</v>
       </c>
       <c r="B10" s="14">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="C10" s="14">
         <v>30</v>
@@ -1304,18 +1313,18 @@
         <v>60</v>
       </c>
       <c r="I10" s="15">
-        <f t="shared" si="0"/>
-        <v>1110</v>
+        <f>IF(SUM(B10:F10,H10)=0,"",SUM(B10:F10,H10))</f>
+        <v>1010</v>
       </c>
       <c r="J10" s="15">
-        <f t="shared" si="1"/>
-        <v>330</v>
+        <f>IF(I10="","",1440-I10)</f>
+        <v>430</v>
       </c>
       <c r="K10" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="L10" s="16" t="s">
         <v>58</v>
-      </c>
-      <c r="L10" s="16" t="s">
-        <v>54</v>
       </c>
       <c r="M10" s="16" t="s">
         <v>55</v>
@@ -1326,62 +1335,62 @@
     </row>
     <row r="11" spans="1:14" ht="15">
       <c r="A11" s="13">
-        <v>46256</v>
+        <v>46255</v>
       </c>
       <c r="B11" s="14">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="C11" s="14">
         <v>30</v>
       </c>
       <c r="D11" s="14">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="E11" s="14">
         <v>60</v>
       </c>
       <c r="F11" s="14">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="G11" s="14">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H11" s="14">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="I11" s="15">
-        <f t="shared" si="0"/>
-        <v>760</v>
+        <f>IF(SUM(B11:F11,H11)=0,"",SUM(B11:F11,H11))</f>
+        <v>1110</v>
       </c>
       <c r="J11" s="15">
-        <f t="shared" si="1"/>
-        <v>680</v>
+        <f>IF(I11="","",1440-I11)</f>
+        <v>330</v>
       </c>
       <c r="K11" s="16" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="L11" s="16" t="s">
         <v>54</v>
       </c>
       <c r="M11" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="N11" s="17" t="s">
         <v>63</v>
-      </c>
-      <c r="N11" s="17" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="12" spans="1:14" ht="15">
       <c r="A12" s="13">
-        <v>46257</v>
+        <v>46256</v>
       </c>
       <c r="B12" s="14">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="C12" s="14">
         <v>30</v>
       </c>
       <c r="D12" s="14">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="E12" s="14">
         <v>60</v>
@@ -1396,29 +1405,29 @@
         <v>90</v>
       </c>
       <c r="I12" s="15">
-        <f t="shared" si="0"/>
-        <v>640</v>
+        <f>IF(SUM(B12:F12,H12)=0,"",SUM(B12:F12,H12))</f>
+        <v>760</v>
       </c>
       <c r="J12" s="15">
-        <f t="shared" si="1"/>
-        <v>800</v>
+        <f>IF(I12="","",1440-I12)</f>
+        <v>680</v>
       </c>
       <c r="K12" s="16" t="s">
         <v>53</v>
       </c>
       <c r="L12" s="16" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="M12" s="16" t="s">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="N12" s="17" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
     </row>
     <row r="13" spans="1:14" ht="15">
       <c r="A13" s="13">
-        <v>46258</v>
+        <v>46257</v>
       </c>
       <c r="B13" s="14">
         <v>400</v>
@@ -1433,41 +1442,41 @@
         <v>60</v>
       </c>
       <c r="F13" s="14">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="G13" s="14">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H13" s="14">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="I13" s="15">
-        <f t="shared" si="0"/>
-        <v>850</v>
+        <f>IF(SUM(B13:F13,H13)=0,"",SUM(B13:F13,H13))</f>
+        <v>640</v>
       </c>
       <c r="J13" s="15">
-        <f t="shared" si="1"/>
-        <v>590</v>
+        <f>IF(I13="","",1440-I13)</f>
+        <v>800</v>
       </c>
       <c r="K13" s="16" t="s">
         <v>53</v>
       </c>
       <c r="L13" s="16" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="M13" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="N13" s="17" t="s">
         <v>63</v>
-      </c>
-      <c r="N13" s="17" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="14" spans="1:14" ht="15">
       <c r="A14" s="13">
-        <v>46259</v>
+        <v>46258</v>
       </c>
       <c r="B14" s="14">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="C14" s="14">
         <v>30</v>
@@ -1479,21 +1488,21 @@
         <v>60</v>
       </c>
       <c r="F14" s="14">
-        <v>250</v>
+        <v>200</v>
       </c>
       <c r="G14" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H14" s="14">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="I14" s="15">
-        <f t="shared" si="0"/>
-        <v>660</v>
+        <f>IF(SUM(B14:F14,H14)=0,"",SUM(B14:F14,H14))</f>
+        <v>850</v>
       </c>
       <c r="J14" s="15">
-        <f t="shared" si="1"/>
-        <v>780</v>
+        <f>IF(I14="","",1440-I14)</f>
+        <v>590</v>
       </c>
       <c r="K14" s="16" t="s">
         <v>53</v>
@@ -1502,7 +1511,7 @@
         <v>54</v>
       </c>
       <c r="M14" s="16" t="s">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="N14" s="17" t="s">
         <v>66</v>
@@ -1510,16 +1519,16 @@
     </row>
     <row r="15" spans="1:14" ht="15">
       <c r="A15" s="13">
-        <v>46260</v>
+        <v>46259</v>
       </c>
       <c r="B15" s="14">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="C15" s="14">
         <v>30</v>
       </c>
       <c r="D15" s="14">
-        <v>200</v>
+        <v>60</v>
       </c>
       <c r="E15" s="14">
         <v>60</v>
@@ -1531,15 +1540,15 @@
         <v>5</v>
       </c>
       <c r="H15" s="14">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="I15" s="15">
-        <f t="shared" si="0"/>
-        <v>960</v>
+        <f>IF(SUM(B15:F15,H15)=0,"",SUM(B15:F15,H15))</f>
+        <v>660</v>
       </c>
       <c r="J15" s="15">
-        <f t="shared" si="1"/>
-        <v>480</v>
+        <f>IF(I15="","",1440-I15)</f>
+        <v>780</v>
       </c>
       <c r="K15" s="16" t="s">
         <v>53</v>
@@ -1548,7 +1557,7 @@
         <v>54</v>
       </c>
       <c r="M15" s="16" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="N15" s="17" t="s">
         <v>67</v>
@@ -1556,10 +1565,10 @@
     </row>
     <row r="16" spans="1:14" ht="15">
       <c r="A16" s="13">
-        <v>46261</v>
+        <v>46260</v>
       </c>
       <c r="B16" s="14">
-        <v>350</v>
+        <v>300</v>
       </c>
       <c r="C16" s="14">
         <v>30</v>
@@ -1571,139 +1580,139 @@
         <v>60</v>
       </c>
       <c r="F16" s="14">
-        <v>300</v>
+        <v>250</v>
       </c>
       <c r="G16" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H16" s="14">
         <v>120</v>
       </c>
       <c r="I16" s="15">
-        <f t="shared" si="0"/>
-        <v>1060</v>
+        <f>IF(SUM(B16:F16,H16)=0,"",SUM(B16:F16,H16))</f>
+        <v>960</v>
       </c>
       <c r="J16" s="15">
-        <f t="shared" si="1"/>
-        <v>380</v>
+        <f>IF(I16="","",1440-I16)</f>
+        <v>480</v>
       </c>
       <c r="K16" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="L16" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="M16" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="N16" s="17" t="s">
         <v>68</v>
-      </c>
-      <c r="L16" s="16" t="s">
-        <v>69</v>
-      </c>
-      <c r="M16" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="N16" s="17" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="17" spans="1:14" ht="15">
       <c r="A17" s="13">
-        <v>46262</v>
+        <v>46261</v>
       </c>
       <c r="B17" s="14">
         <v>350</v>
       </c>
       <c r="C17" s="14">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="D17" s="14">
-        <v>120</v>
+        <v>200</v>
       </c>
       <c r="E17" s="14">
         <v>60</v>
       </c>
       <c r="F17" s="14">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="G17" s="14">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H17" s="14">
         <v>120</v>
       </c>
       <c r="I17" s="15">
-        <f t="shared" si="0"/>
-        <v>895</v>
+        <f>IF(SUM(B17:F17,H17)=0,"",SUM(B17:F17,H17))</f>
+        <v>1060</v>
       </c>
       <c r="J17" s="15">
-        <f t="shared" si="1"/>
-        <v>545</v>
+        <f>IF(I17="","",1440-I17)</f>
+        <v>380</v>
       </c>
       <c r="K17" s="16" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="L17" s="16" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="M17" s="16" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="N17" s="17" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
     </row>
     <row r="18" spans="1:14" ht="15">
       <c r="A18" s="13">
-        <v>46263</v>
+        <v>46262</v>
       </c>
       <c r="B18" s="14">
-        <v>420</v>
+        <v>350</v>
       </c>
       <c r="C18" s="14">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="D18" s="14">
-        <v>200</v>
+        <v>120</v>
       </c>
       <c r="E18" s="14">
         <v>60</v>
       </c>
       <c r="F18" s="14">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="G18" s="14">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H18" s="14">
-        <v>200</v>
+        <v>120</v>
       </c>
       <c r="I18" s="15">
-        <f t="shared" si="0"/>
-        <v>910</v>
+        <f>IF(SUM(B18:F18,H18)=0,"",SUM(B18:F18,H18))</f>
+        <v>895</v>
       </c>
       <c r="J18" s="15">
-        <f t="shared" si="1"/>
-        <v>530</v>
+        <f>IF(I18="","",1440-I18)</f>
+        <v>545</v>
       </c>
       <c r="K18" s="16" t="s">
+        <v>69</v>
+      </c>
+      <c r="L18" s="16" t="s">
+        <v>70</v>
+      </c>
+      <c r="M18" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="N18" s="17" t="s">
         <v>68</v>
-      </c>
-      <c r="L18" s="16" t="s">
-        <v>69</v>
-      </c>
-      <c r="M18" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="N18" s="17" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="19" spans="1:14" ht="15">
       <c r="A19" s="13">
-        <v>46264</v>
+        <v>46263</v>
       </c>
       <c r="B19" s="14">
         <v>420</v>
       </c>
       <c r="C19" s="14">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="D19" s="14">
-        <v>220</v>
+        <v>200</v>
       </c>
       <c r="E19" s="14">
         <v>60</v>
@@ -1715,67 +1724,67 @@
         <v>0</v>
       </c>
       <c r="H19" s="14">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="I19" s="15">
-        <f t="shared" si="0"/>
-        <v>845</v>
+        <f>IF(SUM(B19:F19,H19)=0,"",SUM(B19:F19,H19))</f>
+        <v>910</v>
       </c>
       <c r="J19" s="15">
-        <f t="shared" si="1"/>
-        <v>595</v>
+        <f>IF(I19="","",1440-I19)</f>
+        <v>530</v>
       </c>
       <c r="K19" s="16" t="s">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="L19" s="16" t="s">
-        <v>54</v>
+        <v>70</v>
       </c>
       <c r="M19" s="16" t="s">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="N19" s="17" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="20" spans="1:14" ht="30.75">
+    <row r="20" spans="1:14" ht="15">
       <c r="A20" s="13">
-        <v>46265</v>
+        <v>46264</v>
       </c>
       <c r="B20" s="14">
-        <v>360</v>
+        <v>420</v>
       </c>
       <c r="C20" s="14">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="D20" s="14">
-        <v>200</v>
+        <v>220</v>
       </c>
       <c r="E20" s="14">
         <v>60</v>
       </c>
       <c r="F20" s="14">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G20" s="14">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H20" s="14">
         <v>100</v>
       </c>
       <c r="I20" s="15">
-        <f t="shared" si="0"/>
-        <v>850</v>
+        <f>IF(SUM(B20:F20,H20)=0,"",SUM(B20:F20,H20))</f>
+        <v>845</v>
       </c>
       <c r="J20" s="15">
-        <f t="shared" si="1"/>
-        <v>590</v>
+        <f>IF(I20="","",1440-I20)</f>
+        <v>595</v>
       </c>
       <c r="K20" s="16" t="s">
         <v>58</v>
       </c>
       <c r="L20" s="16" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="M20" s="16" t="s">
         <v>55</v>
@@ -1784,9 +1793,9 @@
         <v>73</v>
       </c>
     </row>
-    <row r="21" spans="1:14" ht="15">
+    <row r="21" spans="1:14" ht="30.75">
       <c r="A21" s="13">
-        <v>46266</v>
+        <v>46265</v>
       </c>
       <c r="B21" s="14">
         <v>360</v>
@@ -1798,47 +1807,47 @@
         <v>200</v>
       </c>
       <c r="E21" s="14">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="F21" s="14">
-        <v>250</v>
+        <v>100</v>
       </c>
       <c r="G21" s="14">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H21" s="14">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="I21" s="15">
-        <f t="shared" si="0"/>
-        <v>1080</v>
+        <f>IF(SUM(B21:F21,H21)=0,"",SUM(B21:F21,H21))</f>
+        <v>850</v>
       </c>
       <c r="J21" s="15">
-        <f t="shared" si="1"/>
-        <v>360</v>
+        <f>IF(I21="","",1440-I21)</f>
+        <v>590</v>
       </c>
       <c r="K21" s="16" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="L21" s="16" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="M21" s="16" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="N21" s="17" t="s">
-        <v>60</v>
+        <v>74</v>
       </c>
     </row>
     <row r="22" spans="1:14" ht="15">
       <c r="A22" s="13">
-        <v>46267</v>
+        <v>46266</v>
       </c>
       <c r="B22" s="14">
-        <v>400</v>
+        <v>360</v>
       </c>
       <c r="C22" s="14">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="D22" s="14">
         <v>200</v>
@@ -1853,15 +1862,15 @@
         <v>5</v>
       </c>
       <c r="H22" s="14">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="I22" s="15">
-        <f t="shared" si="0"/>
-        <v>1165</v>
+        <f>IF(SUM(B22:F22,H22)=0,"",SUM(B22:F22,H22))</f>
+        <v>1080</v>
       </c>
       <c r="J22" s="15">
-        <f t="shared" si="1"/>
-        <v>275</v>
+        <f>IF(I22="","",1440-I22)</f>
+        <v>360</v>
       </c>
       <c r="K22" s="16" t="s">
         <v>53</v>
@@ -1870,21 +1879,21 @@
         <v>54</v>
       </c>
       <c r="M22" s="16" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="N22" s="17" t="s">
-        <v>74</v>
+        <v>61</v>
       </c>
     </row>
     <row r="23" spans="1:14" ht="15">
       <c r="A23" s="13">
-        <v>46268</v>
+        <v>46267</v>
       </c>
       <c r="B23" s="14">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="C23" s="14">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="D23" s="14">
         <v>200</v>
@@ -1893,38 +1902,38 @@
         <v>120</v>
       </c>
       <c r="F23" s="14">
-        <v>300</v>
+        <v>250</v>
       </c>
       <c r="G23" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H23" s="14">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="I23" s="15">
-        <f t="shared" si="0"/>
-        <v>1070</v>
+        <f>IF(SUM(B23:F23,H23)=0,"",SUM(B23:F23,H23))</f>
+        <v>1165</v>
       </c>
       <c r="J23" s="15">
-        <f t="shared" si="1"/>
-        <v>370</v>
+        <f>IF(I23="","",1440-I23)</f>
+        <v>275</v>
       </c>
       <c r="K23" s="16" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="L23" s="16" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="M23" s="16" t="s">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="N23" s="17" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="24" spans="1:14" ht="30.75">
+    <row r="24" spans="1:14" ht="15">
       <c r="A24" s="13">
-        <v>46269</v>
+        <v>46268</v>
       </c>
       <c r="B24" s="14">
         <v>300</v>
@@ -1933,82 +1942,82 @@
         <v>30</v>
       </c>
       <c r="D24" s="14">
-        <v>120</v>
+        <v>200</v>
       </c>
       <c r="E24" s="14">
         <v>120</v>
       </c>
       <c r="F24" s="14">
-        <v>350</v>
+        <v>300</v>
       </c>
       <c r="G24" s="14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H24" s="14">
         <v>120</v>
       </c>
       <c r="I24" s="15">
-        <f t="shared" si="0"/>
-        <v>1040</v>
+        <f>IF(SUM(B24:F24,H24)=0,"",SUM(B24:F24,H24))</f>
+        <v>1070</v>
       </c>
       <c r="J24" s="15">
-        <f t="shared" si="1"/>
-        <v>400</v>
+        <f>IF(I24="","",1440-I24)</f>
+        <v>370</v>
       </c>
       <c r="K24" s="16" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="L24" s="16" t="s">
-        <v>69</v>
+        <v>58</v>
       </c>
       <c r="M24" s="16" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="N24" s="17" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="25" spans="1:14" ht="15">
+    <row r="25" spans="1:14" ht="30.75">
       <c r="A25" s="13">
-        <v>46270</v>
+        <v>46269</v>
       </c>
       <c r="B25" s="14">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="C25" s="14">
         <v>30</v>
       </c>
       <c r="D25" s="14">
-        <v>240</v>
+        <v>120</v>
       </c>
       <c r="E25" s="14">
         <v>120</v>
       </c>
       <c r="F25" s="14">
-        <v>50</v>
+        <v>350</v>
       </c>
       <c r="G25" s="14">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H25" s="14">
-        <v>180</v>
+        <v>120</v>
       </c>
       <c r="I25" s="15">
-        <f t="shared" si="0"/>
-        <v>1020</v>
+        <f>IF(SUM(B25:F25,H25)=0,"",SUM(B25:F25,H25))</f>
+        <v>1040</v>
       </c>
       <c r="J25" s="15">
-        <f t="shared" si="1"/>
-        <v>420</v>
+        <f>IF(I25="","",1440-I25)</f>
+        <v>400</v>
       </c>
       <c r="K25" s="16" t="s">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="L25" s="16" t="s">
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="M25" s="16" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="N25" s="17" t="s">
         <v>77</v>
@@ -2016,45 +2025,45 @@
     </row>
     <row r="26" spans="1:14" ht="15">
       <c r="A26" s="13">
-        <v>46271</v>
+        <v>46270</v>
       </c>
       <c r="B26" s="14">
-        <v>360</v>
+        <v>400</v>
       </c>
       <c r="C26" s="14">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="D26" s="14">
-        <v>300</v>
+        <v>240</v>
       </c>
       <c r="E26" s="14">
         <v>120</v>
       </c>
       <c r="F26" s="14">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="G26" s="14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H26" s="14">
-        <v>120</v>
+        <v>180</v>
       </c>
       <c r="I26" s="15">
-        <f t="shared" si="0"/>
-        <v>945</v>
+        <f>IF(SUM(B26:F26,H26)=0,"",SUM(B26:F26,H26))</f>
+        <v>1020</v>
       </c>
       <c r="J26" s="15">
-        <f t="shared" si="1"/>
-        <v>495</v>
+        <f>IF(I26="","",1440-I26)</f>
+        <v>420</v>
       </c>
       <c r="K26" s="16" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="L26" s="16" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="M26" s="16" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="N26" s="17" t="s">
         <v>78</v>
@@ -2062,36 +2071,36 @@
     </row>
     <row r="27" spans="1:14" ht="15">
       <c r="A27" s="13">
-        <v>46272</v>
+        <v>46271</v>
       </c>
       <c r="B27" s="14">
-        <v>400</v>
+        <v>360</v>
       </c>
       <c r="C27" s="14">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="D27" s="14">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="E27" s="14">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="F27" s="14">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="G27" s="14">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H27" s="14">
         <v>120</v>
       </c>
       <c r="I27" s="15">
-        <f t="shared" si="0"/>
-        <v>1100</v>
+        <f>IF(SUM(B27:F27,H27)=0,"",SUM(B27:F27,H27))</f>
+        <v>945</v>
       </c>
       <c r="J27" s="15">
-        <f t="shared" si="1"/>
-        <v>340</v>
+        <f>IF(I27="","",1440-I27)</f>
+        <v>495</v>
       </c>
       <c r="K27" s="16" t="s">
         <v>53</v>
@@ -2100,7 +2109,7 @@
         <v>54</v>
       </c>
       <c r="M27" s="16" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="N27" s="17" t="s">
         <v>79</v>
@@ -2108,45 +2117,45 @@
     </row>
     <row r="28" spans="1:14" ht="15">
       <c r="A28" s="13">
-        <v>46273</v>
+        <v>46272</v>
       </c>
       <c r="B28" s="14">
-        <v>350</v>
+        <v>400</v>
       </c>
       <c r="C28" s="14">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="D28" s="14">
-        <v>240</v>
+        <v>200</v>
       </c>
       <c r="E28" s="14">
         <v>150</v>
       </c>
       <c r="F28" s="14">
-        <v>250</v>
+        <v>200</v>
       </c>
       <c r="G28" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H28" s="14">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="I28" s="15">
-        <f t="shared" si="0"/>
-        <v>1185</v>
+        <f>IF(SUM(B28:F28,H28)=0,"",SUM(B28:F28,H28))</f>
+        <v>1100</v>
       </c>
       <c r="J28" s="15">
-        <f t="shared" si="1"/>
-        <v>255</v>
+        <f>IF(I28="","",1440-I28)</f>
+        <v>340</v>
       </c>
       <c r="K28" s="16" t="s">
-        <v>68</v>
+        <v>53</v>
       </c>
       <c r="L28" s="16" t="s">
         <v>54</v>
       </c>
       <c r="M28" s="16" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="N28" s="17" t="s">
         <v>80</v>
@@ -2154,7 +2163,7 @@
     </row>
     <row r="29" spans="1:14" ht="15">
       <c r="A29" s="13">
-        <v>46274</v>
+        <v>46273</v>
       </c>
       <c r="B29" s="14">
         <v>350</v>
@@ -2163,10 +2172,10 @@
         <v>45</v>
       </c>
       <c r="D29" s="14">
-        <v>300</v>
+        <v>240</v>
       </c>
       <c r="E29" s="14">
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="F29" s="14">
         <v>250</v>
@@ -2178,21 +2187,21 @@
         <v>150</v>
       </c>
       <c r="I29" s="15">
-        <f t="shared" si="0"/>
-        <v>1155</v>
+        <f>IF(SUM(B29:F29,H29)=0,"",SUM(B29:F29,H29))</f>
+        <v>1185</v>
       </c>
       <c r="J29" s="15">
-        <f t="shared" si="1"/>
-        <v>285</v>
+        <f>IF(I29="","",1440-I29)</f>
+        <v>255</v>
       </c>
       <c r="K29" s="16" t="s">
-        <v>53</v>
+        <v>69</v>
       </c>
       <c r="L29" s="16" t="s">
         <v>54</v>
       </c>
       <c r="M29" s="16" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="N29" s="17" t="s">
         <v>81</v>
@@ -2200,10 +2209,10 @@
     </row>
     <row r="30" spans="1:14" ht="15">
       <c r="A30" s="13">
-        <v>46275</v>
+        <v>46274</v>
       </c>
       <c r="B30" s="14">
-        <v>400</v>
+        <v>350</v>
       </c>
       <c r="C30" s="14">
         <v>45</v>
@@ -2212,33 +2221,33 @@
         <v>300</v>
       </c>
       <c r="E30" s="14">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="F30" s="14">
-        <v>300</v>
+        <v>250</v>
       </c>
       <c r="G30" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H30" s="14">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="I30" s="15">
-        <f t="shared" si="0"/>
-        <v>1285</v>
+        <f>IF(SUM(B30:F30,H30)=0,"",SUM(B30:F30,H30))</f>
+        <v>1155</v>
       </c>
       <c r="J30" s="15">
-        <f t="shared" si="1"/>
-        <v>155</v>
+        <f>IF(I30="","",1440-I30)</f>
+        <v>285</v>
       </c>
       <c r="K30" s="16" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="L30" s="16" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="M30" s="16" t="s">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="N30" s="17" t="s">
         <v>82</v>
@@ -2246,108 +2255,108 @@
     </row>
     <row r="31" spans="1:14" ht="15">
       <c r="A31" s="13">
-        <v>46276</v>
+        <v>46275</v>
       </c>
       <c r="B31" s="14">
-        <v>240</v>
+        <v>400</v>
       </c>
       <c r="C31" s="14">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="D31" s="14">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="E31" s="14">
         <v>120</v>
       </c>
       <c r="F31" s="14">
-        <v>350</v>
+        <v>300</v>
       </c>
       <c r="G31" s="14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H31" s="14">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="I31" s="15">
-        <f t="shared" si="0"/>
-        <v>1040</v>
+        <f>IF(SUM(B31:F31,H31)=0,"",SUM(B31:F31,H31))</f>
+        <v>1285</v>
       </c>
       <c r="J31" s="15">
-        <f t="shared" si="1"/>
-        <v>400</v>
+        <f>IF(I31="","",1440-I31)</f>
+        <v>155</v>
       </c>
       <c r="K31" s="16" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="L31" s="16" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="M31" s="16" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="N31" s="17" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="32" spans="1:14" ht="30.75">
+    <row r="32" spans="1:14" ht="15">
       <c r="A32" s="13">
-        <v>46277</v>
+        <v>46276</v>
       </c>
       <c r="B32" s="14">
-        <v>400</v>
+        <v>240</v>
       </c>
       <c r="C32" s="14">
         <v>30</v>
       </c>
       <c r="D32" s="14">
+        <v>200</v>
+      </c>
+      <c r="E32" s="14">
         <v>120</v>
       </c>
-      <c r="E32" s="14">
-        <v>60</v>
-      </c>
       <c r="F32" s="14">
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="G32" s="14">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H32" s="14">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="I32" s="15">
-        <f t="shared" si="0"/>
-        <v>910</v>
+        <f>IF(SUM(B32:F32,H32)=0,"",SUM(B32:F32,H32))</f>
+        <v>1040</v>
       </c>
       <c r="J32" s="15">
-        <f t="shared" si="1"/>
-        <v>530</v>
+        <f>IF(I32="","",1440-I32)</f>
+        <v>400</v>
       </c>
       <c r="K32" s="16" t="s">
-        <v>68</v>
+        <v>53</v>
       </c>
       <c r="L32" s="16" t="s">
-        <v>69</v>
+        <v>54</v>
       </c>
       <c r="M32" s="16" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="N32" s="17" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="33" spans="1:14" ht="15">
+    <row r="33" spans="1:14" ht="30.75">
       <c r="A33" s="13">
-        <v>46278</v>
+        <v>46277</v>
       </c>
       <c r="B33" s="14">
-        <v>450</v>
+        <v>400</v>
       </c>
       <c r="C33" s="14">
         <v>30</v>
       </c>
       <c r="D33" s="14">
-        <v>240</v>
+        <v>120</v>
       </c>
       <c r="E33" s="14">
         <v>60</v>
@@ -2359,61 +2368,61 @@
         <v>0</v>
       </c>
       <c r="H33" s="14">
-        <v>120</v>
+        <v>300</v>
       </c>
       <c r="I33" s="15">
-        <f t="shared" si="0"/>
-        <v>900</v>
+        <f>IF(SUM(B33:F33,H33)=0,"",SUM(B33:F33,H33))</f>
+        <v>910</v>
       </c>
       <c r="J33" s="15">
-        <f t="shared" si="1"/>
-        <v>540</v>
+        <f>IF(I33="","",1440-I33)</f>
+        <v>530</v>
       </c>
       <c r="K33" s="16" t="s">
-        <v>53</v>
+        <v>69</v>
       </c>
       <c r="L33" s="16" t="s">
-        <v>54</v>
+        <v>70</v>
       </c>
       <c r="M33" s="16" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="N33" s="17" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
     </row>
     <row r="34" spans="1:14" ht="15">
       <c r="A34" s="13">
-        <v>46279</v>
+        <v>46278</v>
       </c>
       <c r="B34" s="14">
-        <v>300</v>
+        <v>450</v>
       </c>
       <c r="C34" s="14">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="D34" s="14">
-        <v>200</v>
+        <v>240</v>
       </c>
       <c r="E34" s="14">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="F34" s="14">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="G34" s="14">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H34" s="14">
-        <v>200</v>
+        <v>120</v>
       </c>
       <c r="I34" s="15">
-        <f t="shared" si="0"/>
-        <v>1040</v>
+        <f>IF(SUM(B34:F34,H34)=0,"",SUM(B34:F34,H34))</f>
+        <v>900</v>
       </c>
       <c r="J34" s="15">
-        <f t="shared" si="1"/>
-        <v>400</v>
+        <f>IF(I34="","",1440-I34)</f>
+        <v>540</v>
       </c>
       <c r="K34" s="16" t="s">
         <v>53</v>
@@ -2422,44 +2431,44 @@
         <v>54</v>
       </c>
       <c r="M34" s="16" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="N34" s="17" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
     </row>
     <row r="35" spans="1:14" ht="15">
       <c r="A35" s="13">
-        <v>46280</v>
+        <v>46279</v>
       </c>
       <c r="B35" s="14">
+        <v>300</v>
+      </c>
+      <c r="C35" s="14">
+        <v>40</v>
+      </c>
+      <c r="D35" s="14">
+        <v>200</v>
+      </c>
+      <c r="E35" s="14">
+        <v>100</v>
+      </c>
+      <c r="F35" s="14">
+        <v>200</v>
+      </c>
+      <c r="G35" s="14">
+        <v>4</v>
+      </c>
+      <c r="H35" s="14">
+        <v>200</v>
+      </c>
+      <c r="I35" s="15">
+        <f>IF(SUM(B35:F35,H35)=0,"",SUM(B35:F35,H35))</f>
+        <v>1040</v>
+      </c>
+      <c r="J35" s="15">
+        <f>IF(I35="","",1440-I35)</f>
         <v>400</v>
-      </c>
-      <c r="C35" s="14">
-        <v>30</v>
-      </c>
-      <c r="D35" s="14">
-        <v>240</v>
-      </c>
-      <c r="E35" s="14">
-        <v>120</v>
-      </c>
-      <c r="F35" s="14">
-        <v>250</v>
-      </c>
-      <c r="G35" s="14">
-        <v>5</v>
-      </c>
-      <c r="H35" s="14">
-        <v>120</v>
-      </c>
-      <c r="I35" s="15">
-        <f t="shared" si="0"/>
-        <v>1160</v>
-      </c>
-      <c r="J35" s="15">
-        <f t="shared" si="1"/>
-        <v>280</v>
       </c>
       <c r="K35" s="16" t="s">
         <v>53</v>
@@ -2468,24 +2477,24 @@
         <v>54</v>
       </c>
       <c r="M35" s="16" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="N35" s="17" t="s">
-        <v>85</v>
+        <v>68</v>
       </c>
     </row>
     <row r="36" spans="1:14" ht="15">
       <c r="A36" s="13">
-        <v>46281</v>
+        <v>46280</v>
       </c>
       <c r="B36" s="14">
-        <v>350</v>
+        <v>400</v>
       </c>
       <c r="C36" s="14">
-        <v>100</v>
+        <v>30</v>
       </c>
       <c r="D36" s="14">
-        <v>200</v>
+        <v>240</v>
       </c>
       <c r="E36" s="14">
         <v>120</v>
@@ -2497,38 +2506,38 @@
         <v>5</v>
       </c>
       <c r="H36" s="14">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="I36" s="15">
-        <f t="shared" si="0"/>
-        <v>1120</v>
+        <f>IF(SUM(B36:F36,H36)=0,"",SUM(B36:F36,H36))</f>
+        <v>1160</v>
       </c>
       <c r="J36" s="15">
-        <f t="shared" si="1"/>
-        <v>320</v>
+        <f>IF(I36="","",1440-I36)</f>
+        <v>280</v>
       </c>
       <c r="K36" s="16" t="s">
-        <v>68</v>
+        <v>53</v>
       </c>
       <c r="L36" s="16" t="s">
-        <v>69</v>
+        <v>54</v>
       </c>
       <c r="M36" s="16" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="N36" s="17" t="s">
-        <v>71</v>
+        <v>86</v>
       </c>
     </row>
     <row r="37" spans="1:14" ht="15">
       <c r="A37" s="13">
-        <v>46282</v>
+        <v>46281</v>
       </c>
       <c r="B37" s="14">
-        <v>320</v>
+        <v>350</v>
       </c>
       <c r="C37" s="14">
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="D37" s="14">
         <v>200</v>
@@ -2537,67 +2546,67 @@
         <v>120</v>
       </c>
       <c r="F37" s="14">
-        <v>300</v>
+        <v>250</v>
       </c>
       <c r="G37" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H37" s="14">
         <v>100</v>
       </c>
       <c r="I37" s="15">
-        <f t="shared" si="0"/>
-        <v>1080</v>
+        <f>IF(SUM(B37:F37,H37)=0,"",SUM(B37:F37,H37))</f>
+        <v>1120</v>
       </c>
       <c r="J37" s="15">
-        <f t="shared" si="1"/>
-        <v>360</v>
+        <f>IF(I37="","",1440-I37)</f>
+        <v>320</v>
       </c>
       <c r="K37" s="16" t="s">
-        <v>53</v>
+        <v>69</v>
       </c>
       <c r="L37" s="16" t="s">
-        <v>54</v>
+        <v>70</v>
       </c>
       <c r="M37" s="16" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="N37" s="17" t="s">
-        <v>86</v>
+        <v>72</v>
       </c>
     </row>
     <row r="38" spans="1:14" ht="15">
       <c r="A38" s="13">
-        <v>46283</v>
+        <v>46282</v>
       </c>
       <c r="B38" s="14">
-        <v>360</v>
+        <v>320</v>
       </c>
       <c r="C38" s="14">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="D38" s="14">
-        <v>120</v>
+        <v>200</v>
       </c>
       <c r="E38" s="14">
         <v>120</v>
       </c>
       <c r="F38" s="14">
-        <v>350</v>
+        <v>300</v>
       </c>
       <c r="G38" s="14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H38" s="14">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="I38" s="15">
-        <f t="shared" si="0"/>
-        <v>1100</v>
+        <f>IF(SUM(B38:F38,H38)=0,"",SUM(B38:F38,H38))</f>
+        <v>1080</v>
       </c>
       <c r="J38" s="15">
-        <f t="shared" si="1"/>
-        <v>340</v>
+        <f>IF(I38="","",1440-I38)</f>
+        <v>360</v>
       </c>
       <c r="K38" s="16" t="s">
         <v>53</v>
@@ -2606,44 +2615,44 @@
         <v>54</v>
       </c>
       <c r="M38" s="16" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="N38" s="17" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
     </row>
     <row r="39" spans="1:14" ht="15">
       <c r="A39" s="13">
-        <v>46284</v>
+        <v>46283</v>
       </c>
       <c r="B39" s="14">
-        <v>450</v>
+        <v>360</v>
       </c>
       <c r="C39" s="14">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="D39" s="14">
-        <v>180</v>
+        <v>120</v>
       </c>
       <c r="E39" s="14">
         <v>120</v>
       </c>
       <c r="F39" s="14">
-        <v>50</v>
+        <v>350</v>
       </c>
       <c r="G39" s="14">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H39" s="14">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="I39" s="15">
-        <f t="shared" si="0"/>
-        <v>995</v>
+        <f>IF(SUM(B39:F39,H39)=0,"",SUM(B39:F39,H39))</f>
+        <v>1100</v>
       </c>
       <c r="J39" s="15">
-        <f t="shared" si="1"/>
-        <v>445</v>
+        <f>IF(I39="","",1440-I39)</f>
+        <v>340</v>
       </c>
       <c r="K39" s="16" t="s">
         <v>53</v>
@@ -2652,44 +2661,44 @@
         <v>54</v>
       </c>
       <c r="M39" s="16" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="N39" s="17" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="40" spans="1:14" ht="30.75">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="40" spans="1:14" ht="15">
       <c r="A40" s="13">
-        <v>46285</v>
+        <v>46284</v>
       </c>
       <c r="B40" s="14">
-        <v>400</v>
+        <v>450</v>
       </c>
       <c r="C40" s="14">
-        <v>100</v>
+        <v>45</v>
       </c>
       <c r="D40" s="14">
-        <v>200</v>
+        <v>180</v>
       </c>
       <c r="E40" s="14">
         <v>120</v>
       </c>
       <c r="F40" s="14">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="G40" s="14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H40" s="14">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="I40" s="15">
-        <f t="shared" si="0"/>
-        <v>1020</v>
+        <f>IF(SUM(B40:F40,H40)=0,"",SUM(B40:F40,H40))</f>
+        <v>995</v>
       </c>
       <c r="J40" s="15">
-        <f t="shared" si="1"/>
-        <v>420</v>
+        <f>IF(I40="","",1440-I40)</f>
+        <v>445</v>
       </c>
       <c r="K40" s="16" t="s">
         <v>53</v>
@@ -2698,44 +2707,44 @@
         <v>54</v>
       </c>
       <c r="M40" s="16" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="N40" s="17" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="41" spans="1:14" ht="15">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="41" spans="1:14" ht="30.75">
       <c r="A41" s="13">
-        <v>46286</v>
+        <v>46285</v>
       </c>
       <c r="B41" s="14">
-        <v>350</v>
+        <v>400</v>
       </c>
       <c r="C41" s="14">
         <v>100</v>
       </c>
       <c r="D41" s="14">
-        <v>180</v>
+        <v>200</v>
       </c>
       <c r="E41" s="14">
         <v>120</v>
       </c>
       <c r="F41" s="14">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="G41" s="14">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H41" s="14">
         <v>200</v>
       </c>
       <c r="I41" s="15">
-        <f t="shared" si="0"/>
-        <v>1150</v>
+        <f>IF(SUM(B41:F41,H41)=0,"",SUM(B41:F41,H41))</f>
+        <v>1020</v>
       </c>
       <c r="J41" s="15">
-        <f t="shared" si="1"/>
-        <v>290</v>
+        <f>IF(I41="","",1440-I41)</f>
+        <v>420</v>
       </c>
       <c r="K41" s="16" t="s">
         <v>53</v>
@@ -2744,18 +2753,18 @@
         <v>54</v>
       </c>
       <c r="M41" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="N41" s="17" t="s">
         <v>88</v>
       </c>
-      <c r="N41" s="17" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="42" spans="1:14" ht="30.75">
+    </row>
+    <row r="42" spans="1:14" ht="15">
       <c r="A42" s="13">
-        <v>46287</v>
+        <v>46286</v>
       </c>
       <c r="B42" s="14">
-        <v>300</v>
+        <v>350</v>
       </c>
       <c r="C42" s="14">
         <v>100</v>
@@ -2767,50 +2776,50 @@
         <v>120</v>
       </c>
       <c r="F42" s="14">
-        <v>250</v>
+        <v>200</v>
       </c>
       <c r="G42" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H42" s="14">
         <v>200</v>
       </c>
       <c r="I42" s="15">
-        <f t="shared" si="0"/>
+        <f>IF(SUM(B42:F42,H42)=0,"",SUM(B42:F42,H42))</f>
         <v>1150</v>
       </c>
       <c r="J42" s="15">
-        <f t="shared" si="1"/>
+        <f>IF(I42="","",1440-I42)</f>
         <v>290</v>
       </c>
       <c r="K42" s="16" t="s">
         <v>53</v>
       </c>
       <c r="L42" s="16" t="s">
-        <v>69</v>
+        <v>54</v>
       </c>
       <c r="M42" s="16" t="s">
-        <v>63</v>
+        <v>89</v>
       </c>
       <c r="N42" s="17" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="43" spans="1:14" ht="15">
+    <row r="43" spans="1:14" ht="30.75">
       <c r="A43" s="13">
-        <v>46288</v>
+        <v>46287</v>
       </c>
       <c r="B43" s="14">
         <v>300</v>
       </c>
       <c r="C43" s="14">
-        <v>45</v>
+        <v>100</v>
       </c>
       <c r="D43" s="14">
+        <v>180</v>
+      </c>
+      <c r="E43" s="14">
         <v>120</v>
-      </c>
-      <c r="E43" s="14">
-        <v>100</v>
       </c>
       <c r="F43" s="14">
         <v>250</v>
@@ -2822,21 +2831,21 @@
         <v>200</v>
       </c>
       <c r="I43" s="15">
-        <f t="shared" si="0"/>
-        <v>1015</v>
+        <f>IF(SUM(B43:F43,H43)=0,"",SUM(B43:F43,H43))</f>
+        <v>1150</v>
       </c>
       <c r="J43" s="15">
-        <f t="shared" si="1"/>
-        <v>425</v>
+        <f>IF(I43="","",1440-I43)</f>
+        <v>290</v>
       </c>
       <c r="K43" s="16" t="s">
         <v>53</v>
       </c>
       <c r="L43" s="16" t="s">
-        <v>54</v>
+        <v>70</v>
       </c>
       <c r="M43" s="16" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="N43" s="17" t="s">
         <v>91</v>
@@ -2844,10 +2853,10 @@
     </row>
     <row r="44" spans="1:14" ht="15">
       <c r="A44" s="13">
-        <v>46289</v>
+        <v>46288</v>
       </c>
       <c r="B44" s="14">
-        <v>350</v>
+        <v>300</v>
       </c>
       <c r="C44" s="14">
         <v>45</v>
@@ -2856,103 +2865,175 @@
         <v>120</v>
       </c>
       <c r="E44" s="14">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="F44" s="14">
-        <v>300</v>
+        <v>250</v>
       </c>
       <c r="G44" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H44" s="14">
         <v>200</v>
       </c>
       <c r="I44" s="15">
+        <f>IF(SUM(B44:F44,H44)=0,"",SUM(B44:F44,H44))</f>
+        <v>1015</v>
+      </c>
+      <c r="J44" s="15">
+        <f>IF(I44="","",1440-I44)</f>
+        <v>425</v>
+      </c>
+      <c r="K44" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="L44" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="M44" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="N44" s="17" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="45" spans="1:14" ht="15">
+      <c r="A45" s="13">
+        <v>46289</v>
+      </c>
+      <c r="B45" s="14">
+        <v>350</v>
+      </c>
+      <c r="C45" s="14">
+        <v>45</v>
+      </c>
+      <c r="D45" s="14">
+        <v>120</v>
+      </c>
+      <c r="E45" s="14">
+        <v>120</v>
+      </c>
+      <c r="F45" s="14">
+        <v>300</v>
+      </c>
+      <c r="G45" s="14">
+        <v>6</v>
+      </c>
+      <c r="H45" s="14">
+        <v>200</v>
+      </c>
+      <c r="I45" s="15">
+        <f>IF(SUM(B45:F45,H45)=0,"",SUM(B45:F45,H45))</f>
+        <v>1135</v>
+      </c>
+      <c r="J45" s="15">
+        <f>IF(I45="","",1440-I45)</f>
+        <v>305</v>
+      </c>
+      <c r="K45" s="16" t="s">
+        <v>69</v>
+      </c>
+      <c r="L45" s="16" t="s">
+        <v>70</v>
+      </c>
+      <c r="M45" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="N45" s="17" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="46" spans="1:14" ht="15">
+      <c r="A46" s="13">
+        <v>46290</v>
+      </c>
+      <c r="B46" s="14">
+        <v>400</v>
+      </c>
+      <c r="C46" s="14">
+        <v>30</v>
+      </c>
+      <c r="D46" s="14">
+        <v>180</v>
+      </c>
+      <c r="E46" s="14">
+        <v>100</v>
+      </c>
+      <c r="F46" s="14">
+        <v>350</v>
+      </c>
+      <c r="G46" s="14">
+        <v>7</v>
+      </c>
+      <c r="H46" s="14">
+        <v>220</v>
+      </c>
+      <c r="I46" s="15">
         <f t="shared" si="0"/>
-        <v>1135</v>
-      </c>
-      <c r="J44" s="15">
+        <v>1280</v>
+      </c>
+      <c r="J46" s="15">
         <f t="shared" si="1"/>
-        <v>305</v>
-      </c>
-      <c r="K44" s="16" t="s">
-        <v>68</v>
-      </c>
-      <c r="L44" s="16" t="s">
+        <v>160</v>
+      </c>
+      <c r="K46" s="16" t="s">
         <v>69</v>
       </c>
-      <c r="M44" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="N44" s="17" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="45" spans="1:14">
-      <c r="A45" s="13"/>
-      <c r="B45" s="14"/>
-      <c r="C45" s="14"/>
-      <c r="D45" s="14"/>
-      <c r="E45" s="14"/>
-      <c r="F45" s="14"/>
-      <c r="G45" s="14"/>
-      <c r="H45" s="14"/>
-      <c r="I45" s="15" t="str">
+      <c r="L46" s="16" t="s">
+        <v>70</v>
+      </c>
+      <c r="M46" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="N46" s="17" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="47" spans="1:14" ht="15">
+      <c r="A47" s="13">
+        <v>46291</v>
+      </c>
+      <c r="B47" s="14">
+        <v>400</v>
+      </c>
+      <c r="C47" s="14">
+        <v>40</v>
+      </c>
+      <c r="D47" s="14">
+        <v>200</v>
+      </c>
+      <c r="E47" s="14">
+        <v>100</v>
+      </c>
+      <c r="F47" s="14">
+        <v>0</v>
+      </c>
+      <c r="G47" s="14">
+        <v>0</v>
+      </c>
+      <c r="H47" s="14">
+        <v>200</v>
+      </c>
+      <c r="I47" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J45" s="15" t="str">
+        <v>940</v>
+      </c>
+      <c r="J47" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K45" s="16"/>
-      <c r="L45" s="16"/>
-      <c r="M45" s="16"/>
-      <c r="N45" s="17"/>
-    </row>
-    <row r="46" spans="1:14">
-      <c r="A46" s="13"/>
-      <c r="B46" s="14"/>
-      <c r="C46" s="14"/>
-      <c r="D46" s="14"/>
-      <c r="E46" s="14"/>
-      <c r="F46" s="14"/>
-      <c r="G46" s="14"/>
-      <c r="H46" s="14"/>
-      <c r="I46" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J46" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K46" s="16"/>
-      <c r="L46" s="16"/>
-      <c r="M46" s="16"/>
-      <c r="N46" s="17"/>
-    </row>
-    <row r="47" spans="1:14">
-      <c r="A47" s="13"/>
-      <c r="B47" s="14"/>
-      <c r="C47" s="14"/>
-      <c r="D47" s="14"/>
-      <c r="E47" s="14"/>
-      <c r="F47" s="14"/>
-      <c r="G47" s="14"/>
-      <c r="H47" s="14"/>
-      <c r="I47" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J47" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K47" s="16"/>
-      <c r="L47" s="16"/>
-      <c r="M47" s="16"/>
-      <c r="N47" s="17"/>
+        <v>500</v>
+      </c>
+      <c r="K47" s="16" t="s">
+        <v>69</v>
+      </c>
+      <c r="L47" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="M47" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="N47" s="17" t="s">
+        <v>94</v>
+      </c>
     </row>
     <row r="48" spans="1:14">
       <c r="A48" s="13"/>

--- a/12622343.xlsx
+++ b/12622343.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30516"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776-26271\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{68D69EC7-6CA4-42AB-9330-B102CD2557C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A5EF1026-5234-43DA-9380-FFB477D01CEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="95">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -3035,29 +3035,53 @@
         <v>94</v>
       </c>
     </row>
-    <row r="48" spans="1:14">
-      <c r="A48" s="13"/>
-      <c r="B48" s="14"/>
-      <c r="C48" s="14"/>
-      <c r="D48" s="14"/>
-      <c r="E48" s="14"/>
-      <c r="F48" s="14"/>
-      <c r="G48" s="14"/>
-      <c r="H48" s="14"/>
-      <c r="I48" s="15" t="str">
+    <row r="48" spans="1:14" ht="15">
+      <c r="A48" s="13">
+        <v>46292</v>
+      </c>
+      <c r="B48" s="14">
+        <v>450</v>
+      </c>
+      <c r="C48" s="14">
+        <v>45</v>
+      </c>
+      <c r="D48" s="14">
+        <v>180</v>
+      </c>
+      <c r="E48" s="14">
+        <v>120</v>
+      </c>
+      <c r="F48" s="14">
+        <v>0</v>
+      </c>
+      <c r="G48" s="14">
+        <v>0</v>
+      </c>
+      <c r="H48" s="14">
+        <v>120</v>
+      </c>
+      <c r="I48" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J48" s="15" t="str">
+        <v>915</v>
+      </c>
+      <c r="J48" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K48" s="16"/>
-      <c r="L48" s="16"/>
-      <c r="M48" s="16"/>
-      <c r="N48" s="17"/>
-    </row>
-    <row r="49" spans="1:14">
+        <v>525</v>
+      </c>
+      <c r="K48" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="L48" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="M48" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="N48" s="17" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="49" spans="1:14" ht="15">
       <c r="A49" s="13"/>
       <c r="B49" s="14"/>
       <c r="C49" s="14"/>
@@ -3066,20 +3090,14 @@
       <c r="F49" s="14"/>
       <c r="G49" s="14"/>
       <c r="H49" s="14"/>
-      <c r="I49" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J49" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
+      <c r="I49" s="15"/>
+      <c r="J49" s="15"/>
       <c r="K49" s="16"/>
       <c r="L49" s="16"/>
       <c r="M49" s="16"/>
       <c r="N49" s="17"/>
     </row>
-    <row r="50" spans="1:14">
+    <row r="50" spans="1:14" ht="15">
       <c r="A50" s="13"/>
       <c r="B50" s="14"/>
       <c r="C50" s="14"/>

--- a/12622343.xlsx
+++ b/12622343.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776-26271\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A5EF1026-5234-43DA-9380-FFB477D01CEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{635947BC-3FD2-4E34-98A9-E2B61A219CAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="96">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -325,6 +325,9 @@
   </si>
   <si>
     <t>Completed a project today</t>
+  </si>
+  <si>
+    <t>Protests going on in the university</t>
   </si>
 </sst>
 </file>
@@ -3081,21 +3084,49 @@
         <v>79</v>
       </c>
     </row>
-    <row r="49" spans="1:14" ht="15">
-      <c r="A49" s="13"/>
-      <c r="B49" s="14"/>
-      <c r="C49" s="14"/>
-      <c r="D49" s="14"/>
-      <c r="E49" s="14"/>
-      <c r="F49" s="14"/>
-      <c r="G49" s="14"/>
-      <c r="H49" s="14"/>
-      <c r="I49" s="15"/>
-      <c r="J49" s="15"/>
-      <c r="K49" s="16"/>
-      <c r="L49" s="16"/>
-      <c r="M49" s="16"/>
-      <c r="N49" s="17"/>
+    <row r="49" spans="1:14" ht="30.75">
+      <c r="A49" s="13">
+        <v>46293</v>
+      </c>
+      <c r="B49" s="14">
+        <v>420</v>
+      </c>
+      <c r="C49" s="14">
+        <v>30</v>
+      </c>
+      <c r="D49" s="14">
+        <v>120</v>
+      </c>
+      <c r="E49" s="14">
+        <v>120</v>
+      </c>
+      <c r="F49" s="14">
+        <v>0</v>
+      </c>
+      <c r="G49" s="14">
+        <v>0</v>
+      </c>
+      <c r="H49" s="14">
+        <v>240</v>
+      </c>
+      <c r="I49" s="15">
+        <v>930</v>
+      </c>
+      <c r="J49" s="15">
+        <v>510</v>
+      </c>
+      <c r="K49" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="L49" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="M49" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="N49" s="17" t="s">
+        <v>95</v>
+      </c>
     </row>
     <row r="50" spans="1:14" ht="15">
       <c r="A50" s="13"/>
@@ -3106,14 +3137,8 @@
       <c r="F50" s="14"/>
       <c r="G50" s="14"/>
       <c r="H50" s="14"/>
-      <c r="I50" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J50" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
+      <c r="I50" s="15"/>
+      <c r="J50" s="15"/>
       <c r="K50" s="16"/>
       <c r="L50" s="16"/>
       <c r="M50" s="16"/>

--- a/12622343.xlsx
+++ b/12622343.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776-26271\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{635947BC-3FD2-4E34-98A9-E2B61A219CAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2C6D2AAD-F1D1-4855-BB67-8783AE83A18D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="97">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -328,6 +328,9 @@
   </si>
   <si>
     <t>Protests going on in the university</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Classes postponed amid protest </t>
   </si>
 </sst>
 </file>
@@ -3128,23 +3131,51 @@
         <v>95</v>
       </c>
     </row>
-    <row r="50" spans="1:14" ht="15">
-      <c r="A50" s="13"/>
-      <c r="B50" s="14"/>
-      <c r="C50" s="14"/>
-      <c r="D50" s="14"/>
-      <c r="E50" s="14"/>
-      <c r="F50" s="14"/>
-      <c r="G50" s="14"/>
-      <c r="H50" s="14"/>
-      <c r="I50" s="15"/>
-      <c r="J50" s="15"/>
-      <c r="K50" s="16"/>
-      <c r="L50" s="16"/>
-      <c r="M50" s="16"/>
-      <c r="N50" s="17"/>
-    </row>
-    <row r="51" spans="1:14">
+    <row r="50" spans="1:14" ht="30.75">
+      <c r="A50" s="13">
+        <v>46294</v>
+      </c>
+      <c r="B50" s="14">
+        <v>400</v>
+      </c>
+      <c r="C50" s="14">
+        <v>30</v>
+      </c>
+      <c r="D50" s="14">
+        <v>150</v>
+      </c>
+      <c r="E50" s="14">
+        <v>100</v>
+      </c>
+      <c r="F50" s="14">
+        <v>0</v>
+      </c>
+      <c r="G50" s="14">
+        <v>0</v>
+      </c>
+      <c r="H50" s="14">
+        <v>240</v>
+      </c>
+      <c r="I50" s="15">
+        <v>920</v>
+      </c>
+      <c r="J50" s="15">
+        <v>510</v>
+      </c>
+      <c r="K50" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="L50" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="M50" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="N50" s="17" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="51" spans="1:14" ht="15">
       <c r="A51" s="13"/>
       <c r="B51" s="14"/>
       <c r="C51" s="14"/>
@@ -3153,14 +3184,8 @@
       <c r="F51" s="14"/>
       <c r="G51" s="14"/>
       <c r="H51" s="14"/>
-      <c r="I51" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J51" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
+      <c r="I51" s="15"/>
+      <c r="J51" s="15"/>
       <c r="K51" s="16"/>
       <c r="L51" s="16"/>
       <c r="M51" s="16"/>

--- a/12622343.xlsx
+++ b/12622343.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776-26271\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2C6D2AAD-F1D1-4855-BB67-8783AE83A18D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{7DF9AF4E-8131-4A0E-8456-1EF399598EDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="97">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -3175,23 +3175,51 @@
         <v>96</v>
       </c>
     </row>
-    <row r="51" spans="1:14" ht="15">
-      <c r="A51" s="13"/>
-      <c r="B51" s="14"/>
-      <c r="C51" s="14"/>
-      <c r="D51" s="14"/>
-      <c r="E51" s="14"/>
-      <c r="F51" s="14"/>
-      <c r="G51" s="14"/>
-      <c r="H51" s="14"/>
-      <c r="I51" s="15"/>
-      <c r="J51" s="15"/>
-      <c r="K51" s="16"/>
-      <c r="L51" s="16"/>
-      <c r="M51" s="16"/>
-      <c r="N51" s="17"/>
-    </row>
-    <row r="52" spans="1:14">
+    <row r="51" spans="1:14" ht="30.75">
+      <c r="A51" s="13">
+        <v>46295</v>
+      </c>
+      <c r="B51" s="14">
+        <v>300</v>
+      </c>
+      <c r="C51" s="14">
+        <v>45</v>
+      </c>
+      <c r="D51" s="14">
+        <v>180</v>
+      </c>
+      <c r="E51" s="14">
+        <v>100</v>
+      </c>
+      <c r="F51" s="14">
+        <v>0</v>
+      </c>
+      <c r="G51" s="14">
+        <v>0</v>
+      </c>
+      <c r="H51" s="14">
+        <v>350</v>
+      </c>
+      <c r="I51" s="15">
+        <v>975</v>
+      </c>
+      <c r="J51" s="15">
+        <v>465</v>
+      </c>
+      <c r="K51" s="16" t="s">
+        <v>69</v>
+      </c>
+      <c r="L51" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="M51" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="N51" s="17" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="52" spans="1:14" ht="15">
       <c r="A52" s="13"/>
       <c r="B52" s="14"/>
       <c r="C52" s="14"/>
@@ -3200,10 +3228,7 @@
       <c r="F52" s="14"/>
       <c r="G52" s="14"/>
       <c r="H52" s="14"/>
-      <c r="I52" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
+      <c r="I52" s="15"/>
       <c r="J52" s="15" t="str">
         <f t="shared" si="1"/>
         <v/>

--- a/12622343.xlsx
+++ b/12622343.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776-26271\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7DF9AF4E-8131-4A0E-8456-1EF399598EDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0D163B70-5928-44C2-8B61-569B00E0972F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="98">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -331,6 +331,9 @@
   </si>
   <si>
     <t xml:space="preserve">Classes postponed amid protest </t>
+  </si>
+  <si>
+    <t>Unsatisfied</t>
   </si>
 </sst>
 </file>
@@ -3220,25 +3223,51 @@
       </c>
     </row>
     <row r="52" spans="1:14" ht="15">
-      <c r="A52" s="13"/>
-      <c r="B52" s="14"/>
-      <c r="C52" s="14"/>
-      <c r="D52" s="14"/>
-      <c r="E52" s="14"/>
-      <c r="F52" s="14"/>
-      <c r="G52" s="14"/>
-      <c r="H52" s="14"/>
-      <c r="I52" s="15"/>
-      <c r="J52" s="15" t="str">
+      <c r="A52" s="13">
+        <v>46296</v>
+      </c>
+      <c r="B52" s="14">
+        <v>400</v>
+      </c>
+      <c r="C52" s="14">
+        <v>30</v>
+      </c>
+      <c r="D52" s="14">
+        <v>180</v>
+      </c>
+      <c r="E52" s="14">
+        <v>100</v>
+      </c>
+      <c r="F52" s="14">
+        <v>0</v>
+      </c>
+      <c r="G52" s="14">
+        <v>0</v>
+      </c>
+      <c r="H52" s="14">
+        <v>200</v>
+      </c>
+      <c r="I52" s="15">
+        <v>910</v>
+      </c>
+      <c r="J52" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K52" s="16"/>
-      <c r="L52" s="16"/>
-      <c r="M52" s="16"/>
-      <c r="N52" s="17"/>
-    </row>
-    <row r="53" spans="1:14">
+        <v>530</v>
+      </c>
+      <c r="K52" s="16" t="s">
+        <v>89</v>
+      </c>
+      <c r="L52" s="16" t="s">
+        <v>97</v>
+      </c>
+      <c r="M52" s="16" t="s">
+        <v>89</v>
+      </c>
+      <c r="N52" s="17" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="53" spans="1:14" ht="15">
       <c r="A53" s="13"/>
       <c r="B53" s="14"/>
       <c r="C53" s="14"/>
@@ -3247,14 +3276,8 @@
       <c r="F53" s="14"/>
       <c r="G53" s="14"/>
       <c r="H53" s="14"/>
-      <c r="I53" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J53" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
+      <c r="I53" s="15"/>
+      <c r="J53" s="15"/>
       <c r="K53" s="16"/>
       <c r="L53" s="16"/>
       <c r="M53" s="16"/>

--- a/12622343.xlsx
+++ b/12622343.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30601"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776-26271\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0D163B70-5928-44C2-8B61-569B00E0972F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A35E55E6-3816-44D6-B4F8-59D41D42B98D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="99">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -334,6 +334,9 @@
   </si>
   <si>
     <t>Unsatisfied</t>
+  </si>
+  <si>
+    <t>Day went welll</t>
   </si>
 </sst>
 </file>
@@ -3268,42 +3271,94 @@
       </c>
     </row>
     <row r="53" spans="1:14" ht="15">
-      <c r="A53" s="13"/>
-      <c r="B53" s="14"/>
-      <c r="C53" s="14"/>
-      <c r="D53" s="14"/>
-      <c r="E53" s="14"/>
-      <c r="F53" s="14"/>
-      <c r="G53" s="14"/>
-      <c r="H53" s="14"/>
-      <c r="I53" s="15"/>
-      <c r="J53" s="15"/>
-      <c r="K53" s="16"/>
-      <c r="L53" s="16"/>
-      <c r="M53" s="16"/>
-      <c r="N53" s="17"/>
-    </row>
-    <row r="54" spans="1:14">
-      <c r="A54" s="13"/>
-      <c r="B54" s="14"/>
-      <c r="C54" s="14"/>
-      <c r="D54" s="14"/>
-      <c r="E54" s="14"/>
-      <c r="F54" s="14"/>
-      <c r="G54" s="14"/>
-      <c r="H54" s="14"/>
-      <c r="I54" s="15" t="str">
+      <c r="A53" s="13">
+        <v>46297</v>
+      </c>
+      <c r="B53" s="14">
+        <v>400</v>
+      </c>
+      <c r="C53" s="14">
+        <v>40</v>
+      </c>
+      <c r="D53" s="14">
+        <v>200</v>
+      </c>
+      <c r="E53" s="14">
+        <v>100</v>
+      </c>
+      <c r="F53" s="14">
+        <v>0</v>
+      </c>
+      <c r="G53" s="14">
+        <v>0</v>
+      </c>
+      <c r="H53" s="14">
+        <v>250</v>
+      </c>
+      <c r="I53" s="15">
+        <v>990</v>
+      </c>
+      <c r="J53" s="15">
+        <v>450</v>
+      </c>
+      <c r="K53" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L53" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="M53" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="N53" s="17" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="54" spans="1:14" ht="15">
+      <c r="A54" s="13">
+        <v>46298</v>
+      </c>
+      <c r="B54" s="14">
+        <v>350</v>
+      </c>
+      <c r="C54" s="14">
+        <v>100</v>
+      </c>
+      <c r="D54" s="14">
+        <v>200</v>
+      </c>
+      <c r="E54" s="14">
+        <v>120</v>
+      </c>
+      <c r="F54" s="14">
+        <v>0</v>
+      </c>
+      <c r="G54" s="14">
+        <v>0</v>
+      </c>
+      <c r="H54" s="14">
+        <v>250</v>
+      </c>
+      <c r="I54" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J54" s="15" t="str">
+        <v>1020</v>
+      </c>
+      <c r="J54" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K54" s="16"/>
-      <c r="L54" s="16"/>
-      <c r="M54" s="16"/>
-      <c r="N54" s="17"/>
+        <v>420</v>
+      </c>
+      <c r="K54" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L54" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="M54" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="N54" s="17" t="s">
+        <v>90</v>
+      </c>
     </row>
     <row r="55" spans="1:14">
       <c r="A55" s="13"/>

--- a/12622343.xlsx
+++ b/12622343.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30601"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30602"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776-26271\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A35E55E6-3816-44D6-B4F8-59D41D42B98D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{FB45BB0B-CF99-4372-8EED-597A099A3727}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="99">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -3360,29 +3360,53 @@
         <v>90</v>
       </c>
     </row>
-    <row r="55" spans="1:14">
-      <c r="A55" s="13"/>
-      <c r="B55" s="14"/>
-      <c r="C55" s="14"/>
-      <c r="D55" s="14"/>
-      <c r="E55" s="14"/>
-      <c r="F55" s="14"/>
-      <c r="G55" s="14"/>
-      <c r="H55" s="14"/>
-      <c r="I55" s="15" t="str">
+    <row r="55" spans="1:14" ht="15">
+      <c r="A55" s="13">
+        <v>46299</v>
+      </c>
+      <c r="B55" s="14">
+        <v>420</v>
+      </c>
+      <c r="C55" s="14">
+        <v>45</v>
+      </c>
+      <c r="D55" s="14">
+        <v>240</v>
+      </c>
+      <c r="E55" s="14">
+        <v>100</v>
+      </c>
+      <c r="F55" s="14">
+        <v>0</v>
+      </c>
+      <c r="G55" s="14">
+        <v>0</v>
+      </c>
+      <c r="H55" s="14">
+        <v>200</v>
+      </c>
+      <c r="I55" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J55" s="15" t="str">
+        <v>1005</v>
+      </c>
+      <c r="J55" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K55" s="16"/>
-      <c r="L55" s="16"/>
-      <c r="M55" s="16"/>
-      <c r="N55" s="17"/>
-    </row>
-    <row r="56" spans="1:14">
+        <v>435</v>
+      </c>
+      <c r="K55" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="L55" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="M55" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="N55" s="17" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="56" spans="1:14" ht="15">
       <c r="A56" s="13"/>
       <c r="B56" s="14"/>
       <c r="C56" s="14"/>

--- a/12622343.xlsx
+++ b/12622343.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776-26271\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FB45BB0B-CF99-4372-8EED-597A099A3727}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{BFE9D2DD-66F1-4A8A-8425-3226B1DB90E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="100">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -337,6 +337,9 @@
   </si>
   <si>
     <t>Day went welll</t>
+  </si>
+  <si>
+    <t>Travelled to Ludhiana today</t>
   </si>
 </sst>
 </file>
@@ -3407,26 +3410,50 @@
       </c>
     </row>
     <row r="56" spans="1:14" ht="15">
-      <c r="A56" s="13"/>
-      <c r="B56" s="14"/>
-      <c r="C56" s="14"/>
-      <c r="D56" s="14"/>
-      <c r="E56" s="14"/>
-      <c r="F56" s="14"/>
-      <c r="G56" s="14"/>
-      <c r="H56" s="14"/>
-      <c r="I56" s="15" t="str">
+      <c r="A56" s="13">
+        <v>46300</v>
+      </c>
+      <c r="B56" s="14">
+        <v>350</v>
+      </c>
+      <c r="C56" s="14">
+        <v>45</v>
+      </c>
+      <c r="D56" s="14">
+        <v>240</v>
+      </c>
+      <c r="E56" s="14">
+        <v>120</v>
+      </c>
+      <c r="F56" s="14">
+        <v>200</v>
+      </c>
+      <c r="G56" s="14">
+        <v>4</v>
+      </c>
+      <c r="H56" s="14">
+        <v>200</v>
+      </c>
+      <c r="I56" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J56" s="15" t="str">
+        <v>1155</v>
+      </c>
+      <c r="J56" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K56" s="16"/>
-      <c r="L56" s="16"/>
-      <c r="M56" s="16"/>
-      <c r="N56" s="17"/>
+        <v>285</v>
+      </c>
+      <c r="K56" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="L56" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="M56" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="N56" s="17" t="s">
+        <v>99</v>
+      </c>
     </row>
     <row r="57" spans="1:14">
       <c r="A57" s="13"/>

--- a/12622343.xlsx
+++ b/12622343.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30602"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30610"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776-26271\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BFE9D2DD-66F1-4A8A-8425-3226B1DB90E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{4AE0A993-4297-4562-9470-7BED673A2B34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="102">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -340,6 +340,12 @@
   </si>
   <si>
     <t>Travelled to Ludhiana today</t>
+  </si>
+  <si>
+    <t>Met my friend after a long time</t>
+  </si>
+  <si>
+    <t>Went for shopping  in ludhiana</t>
   </si>
 </sst>
 </file>
@@ -3455,49 +3461,97 @@
         <v>99</v>
       </c>
     </row>
-    <row r="57" spans="1:14">
-      <c r="A57" s="13"/>
-      <c r="B57" s="14"/>
-      <c r="C57" s="14"/>
-      <c r="D57" s="14"/>
-      <c r="E57" s="14"/>
-      <c r="F57" s="14"/>
-      <c r="G57" s="14"/>
-      <c r="H57" s="14"/>
-      <c r="I57" s="15" t="str">
+    <row r="57" spans="1:14" ht="15">
+      <c r="A57" s="13">
+        <v>46301</v>
+      </c>
+      <c r="B57" s="14">
+        <v>400</v>
+      </c>
+      <c r="C57" s="14">
+        <v>50</v>
+      </c>
+      <c r="D57" s="14">
+        <v>200</v>
+      </c>
+      <c r="E57" s="14">
+        <v>120</v>
+      </c>
+      <c r="F57" s="14">
+        <v>250</v>
+      </c>
+      <c r="G57" s="14">
+        <v>5</v>
+      </c>
+      <c r="H57" s="14">
+        <v>150</v>
+      </c>
+      <c r="I57" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J57" s="15" t="str">
+        <v>1170</v>
+      </c>
+      <c r="J57" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K57" s="16"/>
-      <c r="L57" s="16"/>
-      <c r="M57" s="16"/>
-      <c r="N57" s="17"/>
-    </row>
-    <row r="58" spans="1:14">
-      <c r="A58" s="13"/>
-      <c r="B58" s="14"/>
-      <c r="C58" s="14"/>
-      <c r="D58" s="14"/>
-      <c r="E58" s="14"/>
-      <c r="F58" s="14"/>
-      <c r="G58" s="14"/>
-      <c r="H58" s="14"/>
-      <c r="I58" s="15" t="str">
+        <v>270</v>
+      </c>
+      <c r="K57" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="L57" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="M57" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="N57" s="17" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="58" spans="1:14" ht="15">
+      <c r="A58" s="13">
+        <v>46302</v>
+      </c>
+      <c r="B58" s="14">
+        <v>420</v>
+      </c>
+      <c r="C58" s="14">
+        <v>45</v>
+      </c>
+      <c r="D58" s="14">
+        <v>120</v>
+      </c>
+      <c r="E58" s="14">
+        <v>60</v>
+      </c>
+      <c r="F58" s="14">
+        <v>250</v>
+      </c>
+      <c r="G58" s="14">
+        <v>5</v>
+      </c>
+      <c r="H58" s="14">
+        <v>300</v>
+      </c>
+      <c r="I58" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J58" s="15" t="str">
+        <v>1195</v>
+      </c>
+      <c r="J58" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K58" s="16"/>
-      <c r="L58" s="16"/>
-      <c r="M58" s="16"/>
-      <c r="N58" s="17"/>
+        <v>245</v>
+      </c>
+      <c r="K58" s="16" t="s">
+        <v>69</v>
+      </c>
+      <c r="L58" s="16" t="s">
+        <v>70</v>
+      </c>
+      <c r="M58" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="N58" s="17" t="s">
+        <v>101</v>
+      </c>
     </row>
     <row r="59" spans="1:14">
       <c r="A59" s="13"/>

--- a/12622343.xlsx
+++ b/12622343.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776-26271\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4AE0A993-4297-4562-9470-7BED673A2B34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B1A8263E-D180-4A40-8810-FEADA907565A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="104">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -346,6 +346,12 @@
   </si>
   <si>
     <t>Went for shopping  in ludhiana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Came back to my college hostel </t>
+  </si>
+  <si>
+    <t>Caught fever and cold</t>
   </si>
 </sst>
 </file>
@@ -3553,49 +3559,97 @@
         <v>101</v>
       </c>
     </row>
-    <row r="59" spans="1:14">
-      <c r="A59" s="13"/>
-      <c r="B59" s="14"/>
-      <c r="C59" s="14"/>
-      <c r="D59" s="14"/>
-      <c r="E59" s="14"/>
-      <c r="F59" s="14"/>
-      <c r="G59" s="14"/>
-      <c r="H59" s="14"/>
-      <c r="I59" s="15" t="str">
+    <row r="59" spans="1:14" ht="30.75">
+      <c r="A59" s="13">
+        <v>46303</v>
+      </c>
+      <c r="B59" s="14">
+        <v>400</v>
+      </c>
+      <c r="C59" s="14">
+        <v>30</v>
+      </c>
+      <c r="D59" s="14">
+        <v>150</v>
+      </c>
+      <c r="E59" s="14">
+        <v>120</v>
+      </c>
+      <c r="F59" s="14">
+        <v>300</v>
+      </c>
+      <c r="G59" s="14">
+        <v>6</v>
+      </c>
+      <c r="H59" s="14">
+        <v>200</v>
+      </c>
+      <c r="I59" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J59" s="15" t="str">
+        <v>1200</v>
+      </c>
+      <c r="J59" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K59" s="16"/>
-      <c r="L59" s="16"/>
-      <c r="M59" s="16"/>
-      <c r="N59" s="17"/>
-    </row>
-    <row r="60" spans="1:14">
-      <c r="A60" s="13"/>
-      <c r="B60" s="14"/>
-      <c r="C60" s="14"/>
-      <c r="D60" s="14"/>
-      <c r="E60" s="14"/>
-      <c r="F60" s="14"/>
-      <c r="G60" s="14"/>
-      <c r="H60" s="14"/>
-      <c r="I60" s="15" t="str">
+        <v>240</v>
+      </c>
+      <c r="K59" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="L59" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="M59" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="N59" s="17" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="60" spans="1:14" ht="15">
+      <c r="A60" s="13">
+        <v>46304</v>
+      </c>
+      <c r="B60" s="14">
+        <v>350</v>
+      </c>
+      <c r="C60" s="14">
+        <v>50</v>
+      </c>
+      <c r="D60" s="14">
+        <v>200</v>
+      </c>
+      <c r="E60" s="14">
+        <v>100</v>
+      </c>
+      <c r="F60" s="14">
+        <v>300</v>
+      </c>
+      <c r="G60" s="14">
+        <v>6</v>
+      </c>
+      <c r="H60" s="14">
+        <v>180</v>
+      </c>
+      <c r="I60" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J60" s="15" t="str">
+        <v>1180</v>
+      </c>
+      <c r="J60" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K60" s="16"/>
-      <c r="L60" s="16"/>
-      <c r="M60" s="16"/>
-      <c r="N60" s="17"/>
+        <v>260</v>
+      </c>
+      <c r="K60" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="L60" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="M60" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="N60" s="17" t="s">
+        <v>103</v>
+      </c>
     </row>
     <row r="61" spans="1:14">
       <c r="A61" s="13"/>

--- a/12622343.xlsx
+++ b/12622343.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776-26271\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B1A8263E-D180-4A40-8810-FEADA907565A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A48D2EF7-5299-452B-BE1E-24CC4C1FB028}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="107">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -352,6 +352,15 @@
   </si>
   <si>
     <t>Caught fever and cold</t>
+  </si>
+  <si>
+    <t>Got sick badly</t>
+  </si>
+  <si>
+    <t>Felt Little better from yesterday</t>
+  </si>
+  <si>
+    <t>Had my first MTT today</t>
   </si>
 </sst>
 </file>
@@ -3651,71 +3660,143 @@
         <v>103</v>
       </c>
     </row>
-    <row r="61" spans="1:14">
-      <c r="A61" s="13"/>
-      <c r="B61" s="14"/>
-      <c r="C61" s="14"/>
-      <c r="D61" s="14"/>
-      <c r="E61" s="14"/>
-      <c r="F61" s="14"/>
-      <c r="G61" s="14"/>
-      <c r="H61" s="14"/>
-      <c r="I61" s="15" t="str">
+    <row r="61" spans="1:14" ht="15">
+      <c r="A61" s="13">
+        <v>46305</v>
+      </c>
+      <c r="B61" s="14">
+        <v>500</v>
+      </c>
+      <c r="C61" s="14">
+        <v>0</v>
+      </c>
+      <c r="D61" s="14">
+        <v>60</v>
+      </c>
+      <c r="E61" s="14">
+        <v>0</v>
+      </c>
+      <c r="F61" s="14">
+        <v>0</v>
+      </c>
+      <c r="G61" s="14">
+        <v>0</v>
+      </c>
+      <c r="H61" s="14">
+        <v>0</v>
+      </c>
+      <c r="I61" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J61" s="15" t="str">
+        <v>560</v>
+      </c>
+      <c r="J61" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K61" s="16"/>
-      <c r="L61" s="16"/>
-      <c r="M61" s="16"/>
-      <c r="N61" s="17"/>
-    </row>
-    <row r="62" spans="1:14">
-      <c r="A62" s="13"/>
-      <c r="B62" s="14"/>
-      <c r="C62" s="14"/>
-      <c r="D62" s="14"/>
-      <c r="E62" s="14"/>
-      <c r="F62" s="14"/>
-      <c r="G62" s="14"/>
-      <c r="H62" s="14"/>
-      <c r="I62" s="15" t="str">
+        <v>880</v>
+      </c>
+      <c r="K61" s="16" t="s">
+        <v>89</v>
+      </c>
+      <c r="L61" s="16" t="s">
+        <v>97</v>
+      </c>
+      <c r="M61" s="16" t="s">
+        <v>89</v>
+      </c>
+      <c r="N61" s="17" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="62" spans="1:14" ht="30.75">
+      <c r="A62" s="13">
+        <v>46306</v>
+      </c>
+      <c r="B62" s="14">
+        <v>500</v>
+      </c>
+      <c r="C62" s="14">
+        <v>0</v>
+      </c>
+      <c r="D62" s="14">
+        <v>100</v>
+      </c>
+      <c r="E62" s="14">
+        <v>60</v>
+      </c>
+      <c r="F62" s="14">
+        <v>0</v>
+      </c>
+      <c r="G62" s="14">
+        <v>0</v>
+      </c>
+      <c r="H62" s="14">
+        <v>60</v>
+      </c>
+      <c r="I62" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J62" s="15" t="str">
+        <v>720</v>
+      </c>
+      <c r="J62" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K62" s="16"/>
-      <c r="L62" s="16"/>
-      <c r="M62" s="16"/>
-      <c r="N62" s="17"/>
-    </row>
-    <row r="63" spans="1:14">
-      <c r="A63" s="13"/>
-      <c r="B63" s="14"/>
-      <c r="C63" s="14"/>
-      <c r="D63" s="14"/>
-      <c r="E63" s="14"/>
-      <c r="F63" s="14"/>
-      <c r="G63" s="14"/>
-      <c r="H63" s="14"/>
-      <c r="I63" s="15" t="str">
+        <v>720</v>
+      </c>
+      <c r="K62" s="16" t="s">
+        <v>89</v>
+      </c>
+      <c r="L62" s="16" t="s">
+        <v>97</v>
+      </c>
+      <c r="M62" s="16" t="s">
+        <v>89</v>
+      </c>
+      <c r="N62" s="17" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="63" spans="1:14" ht="15">
+      <c r="A63" s="13">
+        <v>46307</v>
+      </c>
+      <c r="B63" s="14">
+        <v>350</v>
+      </c>
+      <c r="C63" s="14">
+        <v>50</v>
+      </c>
+      <c r="D63" s="14">
+        <v>250</v>
+      </c>
+      <c r="E63" s="14">
+        <v>120</v>
+      </c>
+      <c r="F63" s="14">
+        <v>0</v>
+      </c>
+      <c r="G63" s="14">
+        <v>0</v>
+      </c>
+      <c r="H63" s="14">
+        <v>180</v>
+      </c>
+      <c r="I63" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J63" s="15" t="str">
+        <v>950</v>
+      </c>
+      <c r="J63" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K63" s="16"/>
-      <c r="L63" s="16"/>
-      <c r="M63" s="16"/>
-      <c r="N63" s="17"/>
+        <v>490</v>
+      </c>
+      <c r="K63" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L63" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="M63" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="N63" s="17" t="s">
+        <v>106</v>
+      </c>
     </row>
     <row r="64" spans="1:14">
       <c r="A64" s="13"/>

--- a/12622343.xlsx
+++ b/12622343.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776-26271\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A48D2EF7-5299-452B-BE1E-24CC4C1FB028}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{247D6E74-E8D8-4390-8F3D-E82C08B640C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="109">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -361,6 +361,12 @@
   </si>
   <si>
     <t>Had my first MTT today</t>
+  </si>
+  <si>
+    <t>Second exam went good as well</t>
+  </si>
+  <si>
+    <t>Felt good to spend some time with friends</t>
   </si>
 </sst>
 </file>
@@ -3798,49 +3804,97 @@
         <v>106</v>
       </c>
     </row>
-    <row r="64" spans="1:14">
-      <c r="A64" s="13"/>
-      <c r="B64" s="14"/>
-      <c r="C64" s="14"/>
-      <c r="D64" s="14"/>
-      <c r="E64" s="14"/>
-      <c r="F64" s="14"/>
-      <c r="G64" s="14"/>
-      <c r="H64" s="14"/>
-      <c r="I64" s="15" t="str">
+    <row r="64" spans="1:14" ht="30.75">
+      <c r="A64" s="13">
+        <v>46308</v>
+      </c>
+      <c r="B64" s="14">
+        <v>350</v>
+      </c>
+      <c r="C64" s="14">
+        <v>30</v>
+      </c>
+      <c r="D64" s="14">
+        <v>300</v>
+      </c>
+      <c r="E64" s="14">
+        <v>60</v>
+      </c>
+      <c r="F64" s="14">
+        <v>0</v>
+      </c>
+      <c r="G64" s="14">
+        <v>0</v>
+      </c>
+      <c r="H64" s="14">
+        <v>200</v>
+      </c>
+      <c r="I64" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J64" s="15" t="str">
+        <v>940</v>
+      </c>
+      <c r="J64" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K64" s="16"/>
-      <c r="L64" s="16"/>
-      <c r="M64" s="16"/>
-      <c r="N64" s="17"/>
-    </row>
-    <row r="65" spans="1:14">
-      <c r="A65" s="13"/>
-      <c r="B65" s="14"/>
-      <c r="C65" s="14"/>
-      <c r="D65" s="14"/>
-      <c r="E65" s="14"/>
-      <c r="F65" s="14"/>
-      <c r="G65" s="14"/>
-      <c r="H65" s="14"/>
-      <c r="I65" s="15" t="str">
+        <v>500</v>
+      </c>
+      <c r="K64" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="L64" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="M64" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="N64" s="17" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="65" spans="1:14" ht="30.75">
+      <c r="A65" s="13">
+        <v>46309</v>
+      </c>
+      <c r="B65" s="14">
+        <v>320</v>
+      </c>
+      <c r="C65" s="14">
+        <v>30</v>
+      </c>
+      <c r="D65" s="14">
+        <v>300</v>
+      </c>
+      <c r="E65" s="14">
+        <v>60</v>
+      </c>
+      <c r="F65" s="14">
+        <v>0</v>
+      </c>
+      <c r="G65" s="14">
+        <v>0</v>
+      </c>
+      <c r="H65" s="14">
+        <v>200</v>
+      </c>
+      <c r="I65" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J65" s="15" t="str">
+        <v>910</v>
+      </c>
+      <c r="J65" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K65" s="16"/>
-      <c r="L65" s="16"/>
-      <c r="M65" s="16"/>
-      <c r="N65" s="17"/>
+        <v>530</v>
+      </c>
+      <c r="K65" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="L65" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="M65" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="N65" s="17" t="s">
+        <v>108</v>
+      </c>
     </row>
     <row r="66" spans="1:14">
       <c r="A66" s="13"/>

--- a/12622343.xlsx
+++ b/12622343.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776-26271\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{247D6E74-E8D8-4390-8F3D-E82C08B640C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6DCE8482-B8B5-450B-9C48-4FACC13DDFF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="110">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -367,6 +367,9 @@
   </si>
   <si>
     <t>Felt good to spend some time with friends</t>
+  </si>
+  <si>
+    <t>Today was a preparatory leave</t>
   </si>
 </sst>
 </file>
@@ -3896,27 +3899,51 @@
         <v>108</v>
       </c>
     </row>
-    <row r="66" spans="1:14">
-      <c r="A66" s="13"/>
-      <c r="B66" s="14"/>
-      <c r="C66" s="14"/>
-      <c r="D66" s="14"/>
-      <c r="E66" s="14"/>
-      <c r="F66" s="14"/>
-      <c r="G66" s="14"/>
-      <c r="H66" s="14"/>
-      <c r="I66" s="15" t="str">
+    <row r="66" spans="1:14" ht="15">
+      <c r="A66" s="13">
+        <v>46310</v>
+      </c>
+      <c r="B66" s="14">
+        <v>350</v>
+      </c>
+      <c r="C66" s="14">
+        <v>30</v>
+      </c>
+      <c r="D66" s="14">
+        <v>250</v>
+      </c>
+      <c r="E66" s="14">
+        <v>100</v>
+      </c>
+      <c r="F66" s="14">
+        <v>0</v>
+      </c>
+      <c r="G66" s="14">
+        <v>0</v>
+      </c>
+      <c r="H66" s="14">
+        <v>150</v>
+      </c>
+      <c r="I66" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J66" s="15" t="str">
+        <v>880</v>
+      </c>
+      <c r="J66" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K66" s="16"/>
-      <c r="L66" s="16"/>
-      <c r="M66" s="16"/>
-      <c r="N66" s="17"/>
+        <v>560</v>
+      </c>
+      <c r="K66" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="L66" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="M66" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="N66" s="17" t="s">
+        <v>109</v>
+      </c>
     </row>
     <row r="67" spans="1:14">
       <c r="A67" s="13"/>
